--- a/SpellSystem_v2_ConflictFree (1).xlsx
+++ b/SpellSystem_v2_ConflictFree (1).xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DT_ElementDefinitions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DT_OffensivePhenomena" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DT_ProtectivePhenomena" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DT_UtilityPhenomena" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⚠ Conflict Dashboard" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combo Map Completo" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phenomenon Coverage" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DT_ElementDefinitions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DT_OffensivePhenomena" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="DT_ProtectivePhenomena" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DT_UtilityPhenomena" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="⚠ Conflict Dashboard" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Combo Map Completo" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Phenomenon Coverage" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -163,7 +163,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -185,11 +185,55 @@
         <color rgb="00D5D8DC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D5D8DC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5D8DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5D8DC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D5D8DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5D8DC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5D8DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5D8DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5D8DC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -271,6 +315,8 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1468,7 +1514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1884,337 +1930,349 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Inferno</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>OFF_Inferno</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Inferno</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Explosion</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>OFF_Explosion</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Detonação</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G8" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H8" s="11" t="inlineStr"/>
-      <c r="I8" s="11" t="inlineStr"/>
-      <c r="J8" s="11" t="inlineStr"/>
-      <c r="K8" s="11" t="inlineStr"/>
-      <c r="L8" s="11" t="inlineStr"/>
-      <c r="M8" s="11" t="inlineStr">
-        <is>
-          <t>Fire+Fire</t>
-        </is>
-      </c>
-      <c r="N8" s="11" t="inlineStr">
-        <is>
-          <t>AoE de fogo. Área grande, dano sustentado.</t>
-        </is>
-      </c>
-      <c r="O8" s="11" t="inlineStr">
-        <is>
-          <t>Explosão de chamas em círculo</t>
+      <c r="G8" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr"/>
+      <c r="J8" s="13" t="inlineStr"/>
+      <c r="K8" s="13" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr"/>
+      <c r="M8" s="13" t="inlineStr">
+        <is>
+          <t>Fire+Wind</t>
+        </is>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
+        <is>
+          <t>Explosão violenta. Burst + knockback forte.</t>
+        </is>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
+        <is>
+          <t>Onda de choque com fogo</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Cyclone</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>OFF_Cyclone</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Ciclone</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>OFF_Steam</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Jato de Vapor</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H9" s="13" t="inlineStr"/>
+      <c r="I9" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J9" s="13" t="inlineStr"/>
+      <c r="K9" s="13" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr"/>
+      <c r="M9" s="13" t="inlineStr">
+        <is>
+          <t>Fire+Water</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
+        <is>
+          <t>Cone de vapor. Burn DoT + obscurece visão.</t>
+        </is>
+      </c>
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>Nuvem de vapor branco</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Lava</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>OFF_Lava</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Lótus de Lava</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr"/>
-      <c r="H9" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I9" s="11" t="inlineStr"/>
-      <c r="J9" s="11" t="inlineStr"/>
-      <c r="K9" s="11" t="inlineStr"/>
-      <c r="L9" s="11" t="inlineStr"/>
-      <c r="M9" s="11" t="inlineStr">
-        <is>
-          <t>Wind+Wind</t>
-        </is>
-      </c>
-      <c r="N9" s="11" t="inlineStr">
-        <is>
-          <t>Vórtice que puxa inimigos. CC + dano.</t>
-        </is>
-      </c>
-      <c r="O9" s="11" t="inlineStr">
-        <is>
-          <t>Tornado miniatura</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Deluge</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>OFF_Deluge</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Dilúvio</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="G10" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr"/>
+      <c r="J10" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K10" s="13" t="inlineStr"/>
+      <c r="L10" s="13" t="inlineStr"/>
+      <c r="M10" s="13" t="inlineStr">
+        <is>
+          <t>Fire+Earth</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>Pool de lava persistente. DoT + slow pesado.</t>
+        </is>
+      </c>
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>Magma borbulhante</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>OFF_Plasma</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Arco de Plasma</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>AoE</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr"/>
-      <c r="H10" s="11" t="inlineStr"/>
-      <c r="I10" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J10" s="11" t="inlineStr"/>
-      <c r="K10" s="11" t="inlineStr"/>
-      <c r="L10" s="11" t="inlineStr"/>
-      <c r="M10" s="11" t="inlineStr">
-        <is>
-          <t>Water+Water</t>
-        </is>
-      </c>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>Chuva na área. DoT + slow persistente.</t>
-        </is>
-      </c>
-      <c r="O10" s="11" t="inlineStr">
-        <is>
-          <t>Nuvem escura com chuva</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Quake</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>OFF_Quake</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Tremor</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H11" s="13" t="inlineStr"/>
+      <c r="I11" s="13" t="inlineStr"/>
+      <c r="J11" s="13" t="inlineStr"/>
+      <c r="K11" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L11" s="13" t="inlineStr"/>
+      <c r="M11" s="13" t="inlineStr">
+        <is>
+          <t>Fire+Lightning</t>
+        </is>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>Raio de plasma perfurante. Alto crit.</t>
+        </is>
+      </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>Arco branco-azulado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>HellFire</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>OFF_HellFire</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Fogo Entrópico</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>AoE</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr"/>
-      <c r="H11" s="11" t="inlineStr"/>
-      <c r="I11" s="11" t="inlineStr"/>
-      <c r="J11" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K11" s="11" t="inlineStr"/>
-      <c r="L11" s="11" t="inlineStr"/>
-      <c r="M11" s="11" t="inlineStr">
-        <is>
-          <t>Earth+Earth</t>
-        </is>
-      </c>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>Terremoto. Stun em área + dano.</t>
-        </is>
-      </c>
-      <c r="O11" s="11" t="inlineStr">
-        <is>
-          <t>Rachadura no chão</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>StormBolt</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>OFF_StormBolt</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Trovão</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Orb</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr"/>
+      <c r="J12" s="13" t="inlineStr"/>
+      <c r="K12" s="13" t="inlineStr"/>
+      <c r="L12" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M12" s="13" t="inlineStr">
+        <is>
+          <t>Fire+Reality</t>
+        </is>
+      </c>
+      <c r="N12" s="13" t="inlineStr">
+        <is>
+          <t>Fogo corrompido. DoT ignora resistências.</t>
+        </is>
+      </c>
+      <c r="O12" s="13" t="inlineStr">
+        <is>
+          <t>Chama negra com brilho vermelho</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>IceSpear</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>OFF_IceSpear</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Lança de Gelo</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>AoE</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr"/>
-      <c r="H12" s="11" t="inlineStr"/>
-      <c r="I12" s="11" t="inlineStr"/>
-      <c r="J12" s="11" t="inlineStr"/>
-      <c r="K12" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L12" s="11" t="inlineStr"/>
-      <c r="M12" s="11" t="inlineStr">
-        <is>
-          <t>Lightning+Lightning</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>Raio do céu. AoE compacta, dano alto + stun.</t>
-        </is>
-      </c>
-      <c r="O12" s="11" t="inlineStr">
-        <is>
-          <t>Relâmpago vertical</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Rift</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>OFF_Rift</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Fissura Dimensional</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>AoE</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr"/>
-      <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
-      <c r="J13" s="11" t="inlineStr"/>
-      <c r="K13" s="11" t="inlineStr"/>
-      <c r="L13" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M13" s="11" t="inlineStr">
-        <is>
-          <t>Reality+Reality</t>
-        </is>
-      </c>
-      <c r="N13" s="11" t="inlineStr">
-        <is>
-          <t>Rasga o espaço. Dano + reduz defesas.</t>
-        </is>
-      </c>
-      <c r="O13" s="11" t="inlineStr">
-        <is>
-          <t>Rachadura roxa instável</t>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Orb</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr"/>
+      <c r="H13" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J13" s="13" t="inlineStr"/>
+      <c r="K13" s="13" t="inlineStr"/>
+      <c r="L13" s="13" t="inlineStr"/>
+      <c r="M13" s="13" t="inlineStr">
+        <is>
+          <t>Wind+Water</t>
+        </is>
+      </c>
+      <c r="N13" s="13" t="inlineStr">
+        <is>
+          <t>Projétil perfurante. Freeze curto + crit bônus.</t>
+        </is>
+      </c>
+      <c r="O13" s="13" t="inlineStr">
+        <is>
+          <t>Estaca de gelo cristalino</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Sandstorm</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>OFF_Explosion</t>
+          <t>OFF_Sandstorm</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>Detonação</t>
+          <t>Tempestade de Areia</t>
         </is>
       </c>
       <c r="D14" s="13" t="n">
@@ -2230,46 +2288,46 @@
           <t>AoE</t>
         </is>
       </c>
-      <c r="G14" s="14" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="G14" s="13" t="inlineStr"/>
       <c r="H14" s="14" t="n">
         <v>0.8</v>
       </c>
       <c r="I14" s="13" t="inlineStr"/>
-      <c r="J14" s="13" t="inlineStr"/>
+      <c r="J14" s="14" t="n">
+        <v>0.8</v>
+      </c>
       <c r="K14" s="13" t="inlineStr"/>
       <c r="L14" s="13" t="inlineStr"/>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>Fire+Wind</t>
+          <t>Wind+Earth</t>
         </is>
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
-          <t>Explosão violenta. Burst + knockback forte.</t>
+          <t>Reduz accuracy/visão + dano leve. CC excelente.</t>
         </is>
       </c>
       <c r="O14" s="13" t="inlineStr">
         <is>
-          <t>Onda de choque com fogo</t>
+          <t>Areia girando violentamente</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Steam</t>
+          <t>ChainLightning</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>OFF_Steam</t>
+          <t>OFF_ChainLightning</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Jato de Vapor</t>
+          <t>Relâmpago em Cadeia</t>
         </is>
       </c>
       <c r="D15" s="13" t="n">
@@ -2285,46 +2343,46 @@
           <t>Beam</t>
         </is>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="13" t="inlineStr"/>
+      <c r="H15" s="14" t="n">
         <v>0.8</v>
       </c>
-      <c r="H15" s="13" t="inlineStr"/>
-      <c r="I15" s="14" t="n">
+      <c r="I15" s="13" t="inlineStr"/>
+      <c r="J15" s="13" t="inlineStr"/>
+      <c r="K15" s="14" t="n">
         <v>0.8</v>
       </c>
-      <c r="J15" s="13" t="inlineStr"/>
-      <c r="K15" s="13" t="inlineStr"/>
       <c r="L15" s="13" t="inlineStr"/>
       <c r="M15" s="13" t="inlineStr">
         <is>
-          <t>Fire+Water</t>
+          <t>Wind+Lightning</t>
         </is>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>Cone de vapor. Burn DoT + obscurece visão.</t>
+          <t>Raio pula entre 3 alvos. -30% dano/salto.</t>
         </is>
       </c>
       <c r="O15" s="13" t="inlineStr">
         <is>
-          <t>Nuvem de vapor branco</t>
+          <t>Arcos saltando entre alvos</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Lava</t>
+          <t>VoidStorm</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>OFF_Lava</t>
+          <t>OFF_VoidStorm</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>Lótus de Lava</t>
+          <t>Tempestade do Vazio</t>
         </is>
       </c>
       <c r="D16" s="13" t="n">
@@ -2340,46 +2398,46 @@
           <t>AoE</t>
         </is>
       </c>
-      <c r="G16" s="14" t="n">
+      <c r="G16" s="13" t="inlineStr"/>
+      <c r="H16" s="14" t="n">
         <v>0.8</v>
       </c>
-      <c r="H16" s="13" t="inlineStr"/>
       <c r="I16" s="13" t="inlineStr"/>
-      <c r="J16" s="14" t="n">
+      <c r="J16" s="13" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr"/>
+      <c r="L16" s="14" t="n">
         <v>0.8</v>
       </c>
-      <c r="K16" s="13" t="inlineStr"/>
-      <c r="L16" s="13" t="inlineStr"/>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>Fire+Earth</t>
+          <t>Wind+Reality</t>
         </is>
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
-          <t>Pool de lava persistente. DoT + slow pesado.</t>
+          <t>Distorção gravitacional. Puxa + dano exótico.</t>
         </is>
       </c>
       <c r="O16" s="13" t="inlineStr">
         <is>
-          <t>Magma borbulhante</t>
+          <t>Espaço curvado com sucção</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Mud</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>OFF_Plasma</t>
+          <t>OFF_Mud</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>Arco de Plasma</t>
+          <t>Pântano</t>
         </is>
       </c>
       <c r="D17" s="13" t="n">
@@ -2392,49 +2450,49 @@
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>Beam</t>
-        </is>
-      </c>
-      <c r="G17" s="14" t="n">
+          <t>AoE</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr"/>
+      <c r="H17" s="13" t="inlineStr"/>
+      <c r="I17" s="14" t="n">
         <v>0.8</v>
       </c>
-      <c r="H17" s="13" t="inlineStr"/>
-      <c r="I17" s="13" t="inlineStr"/>
-      <c r="J17" s="13" t="inlineStr"/>
-      <c r="K17" s="14" t="n">
+      <c r="J17" s="14" t="n">
         <v>0.8</v>
       </c>
+      <c r="K17" s="13" t="inlineStr"/>
       <c r="L17" s="13" t="inlineStr"/>
       <c r="M17" s="13" t="inlineStr">
         <is>
-          <t>Fire+Lightning</t>
+          <t>Water+Earth</t>
         </is>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>Raio de plasma perfurante. Alto crit.</t>
+          <t>Lama. Slow extremo + reduz evasão. Dano baixo.</t>
         </is>
       </c>
       <c r="O17" s="13" t="inlineStr">
         <is>
-          <t>Arco branco-azulado</t>
+          <t>Lama escura borbulhando</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>HellFire</t>
+          <t>ElecWater</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>OFF_HellFire</t>
+          <t>OFF_ElecWater</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>Fogo Entrópico</t>
+          <t>Corrente Elétrica</t>
         </is>
       </c>
       <c r="D18" s="13" t="n">
@@ -2447,49 +2505,49 @@
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>Orb</t>
-        </is>
-      </c>
-      <c r="G18" s="14" t="n">
+          <t>AoE</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr"/>
+      <c r="H18" s="13" t="inlineStr"/>
+      <c r="I18" s="14" t="n">
         <v>0.8</v>
       </c>
-      <c r="H18" s="13" t="inlineStr"/>
-      <c r="I18" s="13" t="inlineStr"/>
       <c r="J18" s="13" t="inlineStr"/>
-      <c r="K18" s="13" t="inlineStr"/>
-      <c r="L18" s="14" t="n">
+      <c r="K18" s="14" t="n">
         <v>0.8</v>
       </c>
+      <c r="L18" s="13" t="inlineStr"/>
       <c r="M18" s="13" t="inlineStr">
         <is>
-          <t>Fire+Reality</t>
+          <t>Water+Lightning</t>
         </is>
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
-          <t>Fogo corrompido. DoT ignora resistências.</t>
+          <t>Água eletrificada. Stun área. 2× se Wet.</t>
         </is>
       </c>
       <c r="O18" s="13" t="inlineStr">
         <is>
-          <t>Chama negra com brilho vermelho</t>
+          <t>Poça com arcos elétricos</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>IceSpear</t>
+          <t>Corrosion</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>OFF_IceSpear</t>
+          <t>OFF_Corrosion</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>Lança de Gelo</t>
+          <t>Corrosão</t>
         </is>
       </c>
       <c r="D19" s="13" t="n">
@@ -2502,49 +2560,49 @@
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>Orb</t>
+          <t>AoE</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr"/>
-      <c r="H19" s="14" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="H19" s="13" t="inlineStr"/>
       <c r="I19" s="14" t="n">
         <v>0.8</v>
       </c>
       <c r="J19" s="13" t="inlineStr"/>
       <c r="K19" s="13" t="inlineStr"/>
-      <c r="L19" s="13" t="inlineStr"/>
+      <c r="L19" s="14" t="n">
+        <v>0.8</v>
+      </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
-          <t>Wind+Water</t>
+          <t>Water+Reality</t>
         </is>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
-          <t>Projétil perfurante. Freeze curto + crit bônus.</t>
+          <t>Água corrompida. Reduz armadura + DoT.</t>
         </is>
       </c>
       <c r="O19" s="13" t="inlineStr">
         <is>
-          <t>Estaca de gelo cristalino</t>
+          <t>Líquido púrpura fumegante</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>Sandstorm</t>
+          <t>Magnetize</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>OFF_Sandstorm</t>
+          <t>OFF_Magnetize</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>Tempestade de Areia</t>
+          <t>Magnetismo</t>
         </is>
       </c>
       <c r="D20" s="13" t="n">
@@ -2561,45 +2619,45 @@
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr"/>
-      <c r="H20" s="14" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="H20" s="13" t="inlineStr"/>
       <c r="I20" s="13" t="inlineStr"/>
       <c r="J20" s="14" t="n">
         <v>0.8</v>
       </c>
-      <c r="K20" s="13" t="inlineStr"/>
+      <c r="K20" s="14" t="n">
+        <v>0.8</v>
+      </c>
       <c r="L20" s="13" t="inlineStr"/>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>Wind+Earth</t>
+          <t>Earth+Lightning</t>
         </is>
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
-          <t>Reduz accuracy/visão + dano leve. CC excelente.</t>
+          <t>Puxa inimigos armados. Bônus vs armored.</t>
         </is>
       </c>
       <c r="O20" s="13" t="inlineStr">
         <is>
-          <t>Areia girando violentamente</t>
+          <t>Campo magnético visível</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>ChainLightning</t>
+          <t>Petrify</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>OFF_ChainLightning</t>
+          <t>OFF_Petrify</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>Relâmpago em Cadeia</t>
+          <t>Petrificação</t>
         </is>
       </c>
       <c r="D21" s="13" t="n">
@@ -2612,49 +2670,49 @@
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>Beam</t>
+          <t>Orb</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr"/>
-      <c r="H21" s="14" t="n">
+      <c r="H21" s="13" t="inlineStr"/>
+      <c r="I21" s="13" t="inlineStr"/>
+      <c r="J21" s="14" t="n">
         <v>0.8</v>
       </c>
-      <c r="I21" s="13" t="inlineStr"/>
-      <c r="J21" s="13" t="inlineStr"/>
-      <c r="K21" s="14" t="n">
+      <c r="K21" s="13" t="inlineStr"/>
+      <c r="L21" s="14" t="n">
         <v>0.8</v>
       </c>
-      <c r="L21" s="13" t="inlineStr"/>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>Wind+Lightning</t>
+          <t>Earth+Reality</t>
         </is>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>Raio pula entre 3 alvos. -30% dano/salto.</t>
+          <t>Transforma alvo em pedra. CC forte, dano baixo.</t>
         </is>
       </c>
       <c r="O21" s="13" t="inlineStr">
         <is>
-          <t>Arcos saltando entre alvos</t>
+          <t>Esfera cinza rachada</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>VoidStorm</t>
+          <t>TimeFracture</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>OFF_VoidStorm</t>
+          <t>OFF_TimeFracture</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>Tempestade do Vazio</t>
+          <t>Fratura Temporal</t>
         </is>
       </c>
       <c r="D22" s="13" t="n">
@@ -2667,379 +2725,391 @@
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>AoE</t>
+          <t>Beam</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr"/>
-      <c r="H22" s="14" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="H22" s="13" t="inlineStr"/>
       <c r="I22" s="13" t="inlineStr"/>
       <c r="J22" s="13" t="inlineStr"/>
-      <c r="K22" s="13" t="inlineStr"/>
+      <c r="K22" s="14" t="n">
+        <v>0.8</v>
+      </c>
       <c r="L22" s="14" t="n">
         <v>0.8</v>
       </c>
       <c r="M22" s="13" t="inlineStr">
         <is>
-          <t>Wind+Reality</t>
+          <t>Lightning+Reality</t>
         </is>
       </c>
       <c r="N22" s="13" t="inlineStr">
         <is>
-          <t>Distorção gravitacional. Puxa + dano exótico.</t>
+          <t>Desacelera tempo dos alvos. Slow extremo.</t>
         </is>
       </c>
       <c r="O22" s="13" t="inlineStr">
         <is>
-          <t>Espaço curvado com sucção</t>
+          <t>Raio cromático com frame-skip</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>Mud</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>OFF_Mud</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Pântano</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Pyroclasm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>OFF_Pyroclasm</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Piroclasma</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr"/>
-      <c r="H23" s="13" t="inlineStr"/>
-      <c r="I23" s="14" t="n">
+      <c r="G23" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="J23" s="14" t="n">
+      <c r="H23" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="K23" s="13" t="inlineStr"/>
-      <c r="L23" s="13" t="inlineStr"/>
-      <c r="M23" s="13" t="inlineStr">
-        <is>
-          <t>Water+Earth</t>
-        </is>
-      </c>
-      <c r="N23" s="13" t="inlineStr">
-        <is>
-          <t>Lama. Slow extremo + reduz evasão. Dano baixo.</t>
-        </is>
-      </c>
-      <c r="O23" s="13" t="inlineStr">
-        <is>
-          <t>Lama escura borbulhando</t>
+      <c r="I23" s="15" t="inlineStr"/>
+      <c r="J23" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K23" s="15" t="inlineStr"/>
+      <c r="L23" s="15" t="inlineStr"/>
+      <c r="M23" s="15" t="inlineStr">
+        <is>
+          <t>Fire+Wind+Earth</t>
+        </is>
+      </c>
+      <c r="N23" s="15" t="inlineStr">
+        <is>
+          <t>Erupção: lava + chuva de pedras + knockback.</t>
+        </is>
+      </c>
+      <c r="O23" s="15" t="inlineStr">
+        <is>
+          <t>Coluna de magma com rochas</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>ElecWater</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>OFF_ElecWater</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Corrente Elétrica</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Monsoon</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>OFF_Monsoon</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Monção Flamejante</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F24" s="15" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr"/>
-      <c r="H24" s="13" t="inlineStr"/>
-      <c r="I24" s="14" t="n">
+      <c r="G24" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="J24" s="13" t="inlineStr"/>
-      <c r="K24" s="14" t="n">
+      <c r="H24" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="L24" s="13" t="inlineStr"/>
-      <c r="M24" s="13" t="inlineStr">
-        <is>
-          <t>Water+Lightning</t>
-        </is>
-      </c>
-      <c r="N24" s="13" t="inlineStr">
-        <is>
-          <t>Água eletrificada. Stun área. 2× se Wet.</t>
-        </is>
-      </c>
-      <c r="O24" s="13" t="inlineStr">
-        <is>
-          <t>Poça com arcos elétricos</t>
+      <c r="I24" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J24" s="15" t="inlineStr"/>
+      <c r="K24" s="15" t="inlineStr"/>
+      <c r="L24" s="15" t="inlineStr"/>
+      <c r="M24" s="15" t="inlineStr">
+        <is>
+          <t>Fire+Wind+Water</t>
+        </is>
+      </c>
+      <c r="N24" s="15" t="inlineStr">
+        <is>
+          <t>Tempestade de vapor quente. Burn + Slow em área.</t>
+        </is>
+      </c>
+      <c r="O24" s="15" t="inlineStr">
+        <is>
+          <t>Chuva fumegante com ventos</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>Corrosion</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>OFF_Corrosion</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Corrosão</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>BallLightning</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>OFF_BallLightning</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Relâmpago Globular</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>Orb</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H25" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I25" s="15" t="inlineStr"/>
+      <c r="J25" s="15" t="inlineStr"/>
+      <c r="K25" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L25" s="15" t="inlineStr"/>
+      <c r="M25" s="15" t="inlineStr">
+        <is>
+          <t>Fire+Wind+Lightning</t>
+        </is>
+      </c>
+      <c r="N25" s="15" t="inlineStr">
+        <is>
+          <t>Esfera elétrica errática. Bounce entre alvos + AoE.</t>
+        </is>
+      </c>
+      <c r="O25" s="15" t="inlineStr">
+        <is>
+          <t>Esfera elétrica flutuante</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>MirageStorm</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>OFF_MirageStorm</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Tempestade Ilusória</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G25" s="13" t="inlineStr"/>
-      <c r="H25" s="13" t="inlineStr"/>
-      <c r="I25" s="14" t="n">
+      <c r="G26" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="J25" s="13" t="inlineStr"/>
-      <c r="K25" s="13" t="inlineStr"/>
-      <c r="L25" s="14" t="n">
+      <c r="H26" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="M25" s="13" t="inlineStr">
-        <is>
-          <t>Water+Reality</t>
-        </is>
-      </c>
-      <c r="N25" s="13" t="inlineStr">
-        <is>
-          <t>Água corrompida. Reduz armadura + DoT.</t>
-        </is>
-      </c>
-      <c r="O25" s="13" t="inlineStr">
-        <is>
-          <t>Líquido púrpura fumegante</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>Magnetize</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>OFF_Magnetize</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>Magnetismo</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="I26" s="15" t="inlineStr"/>
+      <c r="J26" s="15" t="inlineStr"/>
+      <c r="K26" s="15" t="inlineStr"/>
+      <c r="L26" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M26" s="15" t="inlineStr">
+        <is>
+          <t>Fire+Wind+Reality</t>
+        </is>
+      </c>
+      <c r="N26" s="15" t="inlineStr">
+        <is>
+          <t>Fogo fantasma: confusão + dano real.</t>
+        </is>
+      </c>
+      <c r="O26" s="15" t="inlineStr">
+        <is>
+          <t>Chamas que mudam de cor</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Geyser</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>OFF_Geyser</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Gêiser</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="F27" s="15" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr"/>
-      <c r="H26" s="13" t="inlineStr"/>
-      <c r="I26" s="13" t="inlineStr"/>
-      <c r="J26" s="14" t="n">
+      <c r="G27" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="K26" s="14" t="n">
+      <c r="H27" s="15" t="inlineStr"/>
+      <c r="I27" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="L26" s="13" t="inlineStr"/>
-      <c r="M26" s="13" t="inlineStr">
-        <is>
-          <t>Earth+Lightning</t>
-        </is>
-      </c>
-      <c r="N26" s="13" t="inlineStr">
-        <is>
-          <t>Puxa inimigos armados. Bônus vs armored.</t>
-        </is>
-      </c>
-      <c r="O26" s="13" t="inlineStr">
-        <is>
-          <t>Campo magnético visível</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>Petrify</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>OFF_Petrify</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>Petrificação</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="J27" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K27" s="15" t="inlineStr"/>
+      <c r="L27" s="15" t="inlineStr"/>
+      <c r="M27" s="15" t="inlineStr">
+        <is>
+          <t>Fire+Water+Earth</t>
+        </is>
+      </c>
+      <c r="N27" s="15" t="inlineStr">
+        <is>
+          <t>Erupção de água fervente do solo. Knockup + burn.</t>
+        </is>
+      </c>
+      <c r="O27" s="15" t="inlineStr">
+        <is>
+          <t>Coluna de água quente do chão</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>StormBrew</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>OFF_StormBrew</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Caldeirão Elétrico</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr">
-        <is>
-          <t>Orb</t>
-        </is>
-      </c>
-      <c r="G27" s="13" t="inlineStr"/>
-      <c r="H27" s="13" t="inlineStr"/>
-      <c r="I27" s="13" t="inlineStr"/>
-      <c r="J27" s="14" t="n">
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>AoE</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="K27" s="13" t="inlineStr"/>
-      <c r="L27" s="14" t="n">
+      <c r="H28" s="15" t="inlineStr"/>
+      <c r="I28" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="M27" s="13" t="inlineStr">
-        <is>
-          <t>Earth+Reality</t>
-        </is>
-      </c>
-      <c r="N27" s="13" t="inlineStr">
-        <is>
-          <t>Transforma alvo em pedra. CC forte, dano baixo.</t>
-        </is>
-      </c>
-      <c r="O27" s="13" t="inlineStr">
-        <is>
-          <t>Esfera cinza rachada</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>TimeFracture</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>OFF_TimeFracture</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Fratura Temporal</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>Beam</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="inlineStr"/>
-      <c r="H28" s="13" t="inlineStr"/>
-      <c r="I28" s="13" t="inlineStr"/>
-      <c r="J28" s="13" t="inlineStr"/>
-      <c r="K28" s="14" t="n">
+      <c r="J28" s="15" t="inlineStr"/>
+      <c r="K28" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="L28" s="14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M28" s="13" t="inlineStr">
-        <is>
-          <t>Lightning+Reality</t>
-        </is>
-      </c>
-      <c r="N28" s="13" t="inlineStr">
-        <is>
-          <t>Desacelera tempo dos alvos. Slow extremo.</t>
-        </is>
-      </c>
-      <c r="O28" s="13" t="inlineStr">
-        <is>
-          <t>Raio cromático com frame-skip</t>
+      <c r="L28" s="15" t="inlineStr"/>
+      <c r="M28" s="15" t="inlineStr">
+        <is>
+          <t>Fire+Water+Lightning</t>
+        </is>
+      </c>
+      <c r="N28" s="15" t="inlineStr">
+        <is>
+          <t>Vapor eletrificado. Burn + Stun em área.</t>
+        </is>
+      </c>
+      <c r="O28" s="15" t="inlineStr">
+        <is>
+          <t>Nuvem de vapor com raios</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>Pyroclasm</t>
+          <t>AcidRain</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>OFF_Pyroclasm</t>
+          <t>OFF_AcidRain</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Piroclasma</t>
+          <t>Chuva Ácida</t>
         </is>
       </c>
       <c r="D29" s="15" t="n">
@@ -3058,45 +3128,45 @@
       <c r="G29" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="H29" s="16" t="n">
+      <c r="H29" s="15" t="inlineStr"/>
+      <c r="I29" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="I29" s="15" t="inlineStr"/>
-      <c r="J29" s="16" t="n">
+      <c r="J29" s="15" t="inlineStr"/>
+      <c r="K29" s="15" t="inlineStr"/>
+      <c r="L29" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="K29" s="15" t="inlineStr"/>
-      <c r="L29" s="15" t="inlineStr"/>
       <c r="M29" s="15" t="inlineStr">
         <is>
-          <t>Fire+Wind+Earth</t>
+          <t>Fire+Water+Reality</t>
         </is>
       </c>
       <c r="N29" s="15" t="inlineStr">
         <is>
-          <t>Erupção: lava + chuva de pedras + knockback.</t>
+          <t>Chuva corrosiva. DoT + reduz armor progressivamente.</t>
         </is>
       </c>
       <c r="O29" s="15" t="inlineStr">
         <is>
-          <t>Coluna de magma com rochas</t>
+          <t>Gotas brilhantes púrpura-vermelhas</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>Monsoon</t>
+          <t>MagmaSurge</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>OFF_Monsoon</t>
+          <t>OFF_MagmaSurge</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Monção Flamejante</t>
+          <t>Surto de Magma</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
@@ -3109,51 +3179,51 @@
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>AoE</t>
+          <t>Beam</t>
         </is>
       </c>
       <c r="G30" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="H30" s="16" t="n">
+      <c r="H30" s="15" t="inlineStr"/>
+      <c r="I30" s="15" t="inlineStr"/>
+      <c r="J30" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="I30" s="16" t="n">
+      <c r="K30" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="J30" s="15" t="inlineStr"/>
-      <c r="K30" s="15" t="inlineStr"/>
       <c r="L30" s="15" t="inlineStr"/>
       <c r="M30" s="15" t="inlineStr">
         <is>
-          <t>Fire+Wind+Water</t>
+          <t>Fire+Earth+Lightning</t>
         </is>
       </c>
       <c r="N30" s="15" t="inlineStr">
         <is>
-          <t>Tempestade de vapor quente. Burn + Slow em área.</t>
+          <t>Lava eletrificada em linha. Perfura + stun.</t>
         </is>
       </c>
       <c r="O30" s="15" t="inlineStr">
         <is>
-          <t>Chuva fumegante com ventos</t>
+          <t>Fluxo de magma com raios</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>BallLightning</t>
+          <t>Hellforge</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>OFF_BallLightning</t>
+          <t>OFF_Hellforge</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Relâmpago Globular</t>
+          <t>Forja Infernal</t>
         </is>
       </c>
       <c r="D31" s="15" t="n">
@@ -3166,51 +3236,51 @@
       </c>
       <c r="F31" s="15" t="inlineStr">
         <is>
-          <t>Orb</t>
+          <t>AoE</t>
         </is>
       </c>
       <c r="G31" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="H31" s="16" t="n">
+      <c r="H31" s="15" t="inlineStr"/>
+      <c r="I31" s="15" t="inlineStr"/>
+      <c r="J31" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="I31" s="15" t="inlineStr"/>
-      <c r="J31" s="15" t="inlineStr"/>
-      <c r="K31" s="16" t="n">
+      <c r="K31" s="15" t="inlineStr"/>
+      <c r="L31" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="L31" s="15" t="inlineStr"/>
       <c r="M31" s="15" t="inlineStr">
         <is>
-          <t>Fire+Wind+Lightning</t>
+          <t>Fire+Earth+Reality</t>
         </is>
       </c>
       <c r="N31" s="15" t="inlineStr">
         <is>
-          <t>Esfera elétrica errática. Bounce entre alvos + AoE.</t>
+          <t>Lava corrompida. Pool + dano exótico DoT.</t>
         </is>
       </c>
       <c r="O31" s="15" t="inlineStr">
         <is>
-          <t>Esfera elétrica flutuante</t>
+          <t>Lava negra com brilho roxo</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>MirageStorm</t>
+          <t>Antimatter</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>OFF_MirageStorm</t>
+          <t>OFF_Antimatter</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Tempestade Ilusória</t>
+          <t>Antimatéria</t>
         </is>
       </c>
       <c r="D32" s="15" t="n">
@@ -3223,51 +3293,51 @@
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>AoE</t>
+          <t>Orb</t>
         </is>
       </c>
       <c r="G32" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="H32" s="16" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="H32" s="15" t="inlineStr"/>
       <c r="I32" s="15" t="inlineStr"/>
       <c r="J32" s="15" t="inlineStr"/>
-      <c r="K32" s="15" t="inlineStr"/>
+      <c r="K32" s="16" t="n">
+        <v>0.8</v>
+      </c>
       <c r="L32" s="16" t="n">
         <v>0.8</v>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>Fire+Wind+Reality</t>
+          <t>Fire+Lightning+Reality</t>
         </is>
       </c>
       <c r="N32" s="15" t="inlineStr">
         <is>
-          <t>Fogo fantasma: confusão + dano real.</t>
+          <t>Aniquilação. Dano massivo single-target.</t>
         </is>
       </c>
       <c r="O32" s="15" t="inlineStr">
         <is>
-          <t>Chamas que mudam de cor</t>
+          <t>Esfera negra com anel branco</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>Geyser</t>
+          <t>Landslide</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>OFF_Geyser</t>
+          <t>OFF_Landslide</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Gêiser</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D33" s="15" t="n">
@@ -3283,10 +3353,10 @@
           <t>AoE</t>
         </is>
       </c>
-      <c r="G33" s="16" t="n">
+      <c r="G33" s="15" t="inlineStr"/>
+      <c r="H33" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="H33" s="15" t="inlineStr"/>
       <c r="I33" s="16" t="n">
         <v>0.8</v>
       </c>
@@ -3297,34 +3367,34 @@
       <c r="L33" s="15" t="inlineStr"/>
       <c r="M33" s="15" t="inlineStr">
         <is>
-          <t>Fire+Water+Earth</t>
+          <t>Wind+Water+Earth</t>
         </is>
       </c>
       <c r="N33" s="15" t="inlineStr">
         <is>
-          <t>Erupção de água fervente do solo. Knockup + burn.</t>
+          <t>Deslizamento de lama com vento. Knockback + slow.</t>
         </is>
       </c>
       <c r="O33" s="15" t="inlineStr">
         <is>
-          <t>Coluna de água quente do chão</t>
+          <t>Onda de lama com detritos</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>StormBrew</t>
+          <t>Supercell</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>OFF_StormBrew</t>
+          <t>OFF_Supercell</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Caldeirão Elétrico</t>
+          <t>Supercélula</t>
         </is>
       </c>
       <c r="D34" s="15" t="n">
@@ -3340,10 +3410,10 @@
           <t>AoE</t>
         </is>
       </c>
-      <c r="G34" s="16" t="n">
+      <c r="G34" s="15" t="inlineStr"/>
+      <c r="H34" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="H34" s="15" t="inlineStr"/>
       <c r="I34" s="16" t="n">
         <v>0.8</v>
       </c>
@@ -3354,34 +3424,34 @@
       <c r="L34" s="15" t="inlineStr"/>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>Fire+Water+Lightning</t>
+          <t>Wind+Water+Lightning</t>
         </is>
       </c>
       <c r="N34" s="15" t="inlineStr">
         <is>
-          <t>Vapor eletrificado. Burn + Stun em área.</t>
+          <t>Tempestade perfeita: granizo+vento+raios.</t>
         </is>
       </c>
       <c r="O34" s="15" t="inlineStr">
         <is>
-          <t>Nuvem de vapor com raios</t>
+          <t>Nuvem massiva com relâmpagos</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>AcidRain</t>
+          <t>BlackIce</t>
         </is>
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>OFF_AcidRain</t>
+          <t>OFF_BlackIce</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Chuva Ácida</t>
+          <t>Gelo Negro</t>
         </is>
       </c>
       <c r="D35" s="15" t="n">
@@ -3394,13 +3464,13 @@
       </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
-          <t>AoE</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="n">
+          <t>Orb</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr"/>
+      <c r="H35" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="H35" s="15" t="inlineStr"/>
       <c r="I35" s="16" t="n">
         <v>0.8</v>
       </c>
@@ -3411,34 +3481,34 @@
       </c>
       <c r="M35" s="15" t="inlineStr">
         <is>
-          <t>Fire+Water+Reality</t>
+          <t>Wind+Water+Reality</t>
         </is>
       </c>
       <c r="N35" s="15" t="inlineStr">
         <is>
-          <t>Chuva corrosiva. DoT + reduz armor progressivamente.</t>
+          <t>Gelo corrompido. Freeze + dano ignora res.</t>
         </is>
       </c>
       <c r="O35" s="15" t="inlineStr">
         <is>
-          <t>Gotas brilhantes púrpura-vermelhas</t>
+          <t>Cristal negro transparente</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>MagmaSurge</t>
+          <t>Tectonic</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>OFF_MagmaSurge</t>
+          <t>OFF_Tectonic</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Surto de Magma</t>
+          <t>Pulso Tectônico</t>
         </is>
       </c>
       <c r="D36" s="15" t="n">
@@ -3451,13 +3521,13 @@
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>Beam</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="n">
+          <t>AoE</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr"/>
+      <c r="H36" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="H36" s="15" t="inlineStr"/>
       <c r="I36" s="15" t="inlineStr"/>
       <c r="J36" s="16" t="n">
         <v>0.8</v>
@@ -3468,34 +3538,34 @@
       <c r="L36" s="15" t="inlineStr"/>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>Fire+Earth+Lightning</t>
+          <t>Wind+Earth+Lightning</t>
         </is>
       </c>
       <c r="N36" s="15" t="inlineStr">
         <is>
-          <t>Lava eletrificada em linha. Perfura + stun.</t>
+          <t>Onda eletromagnética no solo. Stun área.</t>
         </is>
       </c>
       <c r="O36" s="15" t="inlineStr">
         <is>
-          <t>Fluxo de magma com raios</t>
+          <t>Rachadura com eletricidade</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>Hellforge</t>
+          <t>GravityCrush</t>
         </is>
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>OFF_Hellforge</t>
+          <t>OFF_GravityCrush</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Forja Infernal</t>
+          <t>Esmagamento Gravitacional</t>
         </is>
       </c>
       <c r="D37" s="15" t="n">
@@ -3511,10 +3581,10 @@
           <t>AoE</t>
         </is>
       </c>
-      <c r="G37" s="16" t="n">
+      <c r="G37" s="15" t="inlineStr"/>
+      <c r="H37" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="H37" s="15" t="inlineStr"/>
       <c r="I37" s="15" t="inlineStr"/>
       <c r="J37" s="16" t="n">
         <v>0.8</v>
@@ -3525,34 +3595,34 @@
       </c>
       <c r="M37" s="15" t="inlineStr">
         <is>
-          <t>Fire+Earth+Reality</t>
+          <t>Wind+Earth+Reality</t>
         </is>
       </c>
       <c r="N37" s="15" t="inlineStr">
         <is>
-          <t>Lava corrompida. Pool + dano exótico DoT.</t>
+          <t>Compressão gravitacional. Slow + crush dmg.</t>
         </is>
       </c>
       <c r="O37" s="15" t="inlineStr">
         <is>
-          <t>Lava negra com brilho roxo</t>
+          <t>Espaço se comprimindo sobre alvos</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>Antimatter</t>
+          <t>ChaosStorm</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>OFF_Antimatter</t>
+          <t>OFF_ChaosStorm</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Antimatéria</t>
+          <t>Tempestade Caótica</t>
         </is>
       </c>
       <c r="D38" s="15" t="n">
@@ -3565,13 +3635,13 @@
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>Orb</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="n">
+          <t>AoE</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr"/>
+      <c r="H38" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="H38" s="15" t="inlineStr"/>
       <c r="I38" s="15" t="inlineStr"/>
       <c r="J38" s="15" t="inlineStr"/>
       <c r="K38" s="16" t="n">
@@ -3582,34 +3652,34 @@
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>Fire+Lightning+Reality</t>
+          <t>Wind+Lightning+Reality</t>
         </is>
       </c>
       <c r="N38" s="15" t="inlineStr">
         <is>
-          <t>Aniquilação. Dano massivo single-target.</t>
+          <t>Tempestade de realidade quebrada. Efeitos aleatórios.</t>
         </is>
       </c>
       <c r="O38" s="15" t="inlineStr">
         <is>
-          <t>Esfera negra com anel branco</t>
+          <t>Vórtice com raios e distorções</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>Landslide</t>
+          <t>Quicksand</t>
         </is>
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>OFF_Landslide</t>
+          <t>OFF_Quicksand</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Areia Movediça</t>
         </is>
       </c>
       <c r="D39" s="15" t="n">
@@ -3626,47 +3696,47 @@
         </is>
       </c>
       <c r="G39" s="15" t="inlineStr"/>
-      <c r="H39" s="16" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="H39" s="15" t="inlineStr"/>
       <c r="I39" s="16" t="n">
         <v>0.8</v>
       </c>
       <c r="J39" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="K39" s="15" t="inlineStr"/>
+      <c r="K39" s="16" t="n">
+        <v>0.8</v>
+      </c>
       <c r="L39" s="15" t="inlineStr"/>
       <c r="M39" s="15" t="inlineStr">
         <is>
-          <t>Wind+Water+Earth</t>
+          <t>Water+Earth+Lightning</t>
         </is>
       </c>
       <c r="N39" s="15" t="inlineStr">
         <is>
-          <t>Deslizamento de lama com vento. Knockback + slow.</t>
+          <t>Lama eletrificada. Root + shock DoT.</t>
         </is>
       </c>
       <c r="O39" s="15" t="inlineStr">
         <is>
-          <t>Onda de lama com detritos</t>
+          <t>Lama com faíscas elétricas</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>Supercell</t>
+          <t>Abyss</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>OFF_Supercell</t>
+          <t>OFF_Abyss</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Supercélula</t>
+          <t>Abismo</t>
         </is>
       </c>
       <c r="D40" s="15" t="n">
@@ -3683,47 +3753,47 @@
         </is>
       </c>
       <c r="G40" s="15" t="inlineStr"/>
-      <c r="H40" s="16" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="H40" s="15" t="inlineStr"/>
       <c r="I40" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="J40" s="15" t="inlineStr"/>
-      <c r="K40" s="16" t="n">
+      <c r="J40" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="L40" s="15" t="inlineStr"/>
+      <c r="K40" s="15" t="inlineStr"/>
+      <c r="L40" s="16" t="n">
+        <v>0.8</v>
+      </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>Wind+Water+Lightning</t>
+          <t>Water+Earth+Reality</t>
         </is>
       </c>
       <c r="N40" s="15" t="inlineStr">
         <is>
-          <t>Tempestade perfeita: granizo+vento+raios.</t>
+          <t>Pool de vazio líquido. Pull + dano exótico.</t>
         </is>
       </c>
       <c r="O40" s="15" t="inlineStr">
         <is>
-          <t>Nuvem massiva com relâmpagos</t>
+          <t>Poça negra infinitamente profunda</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>BlackIce</t>
+          <t>VoidCurrent</t>
         </is>
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>OFF_BlackIce</t>
+          <t>OFF_VoidCurrent</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Gelo Negro</t>
+          <t>Corrente do Vazio</t>
         </is>
       </c>
       <c r="D41" s="15" t="n">
@@ -3736,51 +3806,51 @@
       </c>
       <c r="F41" s="15" t="inlineStr">
         <is>
-          <t>Orb</t>
+          <t>Beam</t>
         </is>
       </c>
       <c r="G41" s="15" t="inlineStr"/>
-      <c r="H41" s="16" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="H41" s="15" t="inlineStr"/>
       <c r="I41" s="16" t="n">
         <v>0.8</v>
       </c>
       <c r="J41" s="15" t="inlineStr"/>
-      <c r="K41" s="15" t="inlineStr"/>
+      <c r="K41" s="16" t="n">
+        <v>0.8</v>
+      </c>
       <c r="L41" s="16" t="n">
         <v>0.8</v>
       </c>
       <c r="M41" s="15" t="inlineStr">
         <is>
-          <t>Wind+Water+Reality</t>
+          <t>Water+Lightning+Reality</t>
         </is>
       </c>
       <c r="N41" s="15" t="inlineStr">
         <is>
-          <t>Gelo corrompido. Freeze + dano ignora res.</t>
+          <t>Raio aquático corrompido. Chain + debuff.</t>
         </is>
       </c>
       <c r="O41" s="15" t="inlineStr">
         <is>
-          <t>Cristal negro transparente</t>
+          <t>Raio azul-púrpura fluido</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>Tectonic</t>
+          <t>DimAnchor</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>OFF_Tectonic</t>
+          <t>OFF_DimAnchor</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Pulso Tectônico</t>
+          <t>Âncora Dimensional</t>
         </is>
       </c>
       <c r="D42" s="15" t="n">
@@ -3797,9 +3867,7 @@
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr"/>
-      <c r="H42" s="16" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="H42" s="15" t="inlineStr"/>
       <c r="I42" s="15" t="inlineStr"/>
       <c r="J42" s="16" t="n">
         <v>0.8</v>
@@ -3807,764 +3875,806 @@
       <c r="K42" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="L42" s="15" t="inlineStr"/>
+      <c r="L42" s="16" t="n">
+        <v>0.8</v>
+      </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>Wind+Earth+Lightning</t>
+          <t>Earth+Lightning+Reality</t>
         </is>
       </c>
       <c r="N42" s="15" t="inlineStr">
         <is>
-          <t>Onda eletromagnética no solo. Stun área.</t>
+          <t>Fixa inimigos na dimensão. Root + dmg exótico.</t>
         </is>
       </c>
       <c r="O42" s="15" t="inlineStr">
         <is>
-          <t>Rachadura com eletricidade</t>
+          <t>Correntes de energia no chão</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>GravityCrush</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>OFF_GravityCrush</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="inlineStr">
-        <is>
-          <t>Esmagamento Gravitacional</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>PrimordialTempest</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>OFF_PrimordialTempest</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>Tempestade Primordial</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>Supreme</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G43" s="15" t="inlineStr"/>
-      <c r="H43" s="16" t="n">
+      <c r="G43" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="I43" s="15" t="inlineStr"/>
-      <c r="J43" s="16" t="n">
+      <c r="H43" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="K43" s="15" t="inlineStr"/>
-      <c r="L43" s="16" t="n">
+      <c r="I43" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="M43" s="15" t="inlineStr">
-        <is>
-          <t>Wind+Earth+Reality</t>
-        </is>
-      </c>
-      <c r="N43" s="15" t="inlineStr">
-        <is>
-          <t>Compressão gravitacional. Slow + crush dmg.</t>
-        </is>
-      </c>
-      <c r="O43" s="15" t="inlineStr">
-        <is>
-          <t>Espaço se comprimindo sobre alvos</t>
+      <c r="J43" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K43" s="19" t="inlineStr"/>
+      <c r="L43" s="19" t="inlineStr"/>
+      <c r="M43" s="19" t="inlineStr">
+        <is>
+          <t>Fire+Wind+Water+Earth</t>
+        </is>
+      </c>
+      <c r="N43" s="19" t="inlineStr">
+        <is>
+          <t>Os 4 elementos naturais. Caos total: fogo+gelo+vento+terra.</t>
+        </is>
+      </c>
+      <c r="O43" s="19" t="inlineStr">
+        <is>
+          <t>Vórtice com 4 elementos visíveis</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>ChaosStorm</t>
-        </is>
-      </c>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>OFF_ChaosStorm</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>Tempestade Caótica</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="E44" s="15" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>TyphoonInfernal</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>OFF_TyphoonInfernal</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>Tufão Infernal</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>Supreme</t>
+        </is>
+      </c>
+      <c r="F44" s="19" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G44" s="15" t="inlineStr"/>
-      <c r="H44" s="16" t="n">
+      <c r="G44" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="I44" s="15" t="inlineStr"/>
-      <c r="J44" s="15" t="inlineStr"/>
-      <c r="K44" s="16" t="n">
+      <c r="H44" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="L44" s="16" t="n">
+      <c r="I44" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="M44" s="15" t="inlineStr">
-        <is>
-          <t>Wind+Lightning+Reality</t>
-        </is>
-      </c>
-      <c r="N44" s="15" t="inlineStr">
-        <is>
-          <t>Tempestade de realidade quebrada. Efeitos aleatórios.</t>
-        </is>
-      </c>
-      <c r="O44" s="15" t="inlineStr">
-        <is>
-          <t>Vórtice com raios e distorções</t>
+      <c r="J44" s="19" t="inlineStr"/>
+      <c r="K44" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L44" s="19" t="inlineStr"/>
+      <c r="M44" s="19" t="inlineStr">
+        <is>
+          <t>Fire+Wind+Water+Lightning</t>
+        </is>
+      </c>
+      <c r="N44" s="19" t="inlineStr">
+        <is>
+          <t>Mega-tempestade flamejante. Burn+Slow+Stun rotativos.</t>
+        </is>
+      </c>
+      <c r="O44" s="19" t="inlineStr">
+        <is>
+          <t>Furacão de fogo com raios</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>Quicksand</t>
-        </is>
-      </c>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t>OFF_Quicksand</t>
-        </is>
-      </c>
-      <c r="C45" s="15" t="inlineStr">
-        <is>
-          <t>Areia Movediça</t>
-        </is>
-      </c>
-      <c r="D45" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="E45" s="15" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>ElementalRift</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>OFF_ElementalRift</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>Fenda Elemental</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>Supreme</t>
+        </is>
+      </c>
+      <c r="F45" s="19" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G45" s="15" t="inlineStr"/>
-      <c r="H45" s="15" t="inlineStr"/>
-      <c r="I45" s="16" t="n">
+      <c r="G45" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="J45" s="16" t="n">
+      <c r="H45" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="K45" s="16" t="n">
+      <c r="I45" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="L45" s="15" t="inlineStr"/>
-      <c r="M45" s="15" t="inlineStr">
-        <is>
-          <t>Water+Earth+Lightning</t>
-        </is>
-      </c>
-      <c r="N45" s="15" t="inlineStr">
-        <is>
-          <t>Lama eletrificada. Root + shock DoT.</t>
-        </is>
-      </c>
-      <c r="O45" s="15" t="inlineStr">
-        <is>
-          <t>Lama com faíscas elétricas</t>
+      <c r="J45" s="19" t="inlineStr"/>
+      <c r="K45" s="19" t="inlineStr"/>
+      <c r="L45" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M45" s="19" t="inlineStr">
+        <is>
+          <t>Fire+Wind+Water+Reality</t>
+        </is>
+      </c>
+      <c r="N45" s="19" t="inlineStr">
+        <is>
+          <t>Fenda na realidade. Elementos brotam caoticamente.</t>
+        </is>
+      </c>
+      <c r="O45" s="19" t="inlineStr">
+        <is>
+          <t>Rasgo no ar com água, fogo e vento</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Abyss</t>
-        </is>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>OFF_Abyss</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>Abismo</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>Ragnarok</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>OFF_Ragnarok</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>Ragnarök</t>
+        </is>
+      </c>
+      <c r="D46" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>Supreme</t>
+        </is>
+      </c>
+      <c r="F46" s="19" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G46" s="15" t="inlineStr"/>
-      <c r="H46" s="15" t="inlineStr"/>
-      <c r="I46" s="16" t="n">
+      <c r="G46" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="J46" s="16" t="n">
+      <c r="H46" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="K46" s="15" t="inlineStr"/>
-      <c r="L46" s="16" t="n">
+      <c r="I46" s="19" t="inlineStr"/>
+      <c r="J46" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="M46" s="15" t="inlineStr">
-        <is>
-          <t>Water+Earth+Reality</t>
-        </is>
-      </c>
-      <c r="N46" s="15" t="inlineStr">
-        <is>
-          <t>Pool de vazio líquido. Pull + dano exótico.</t>
-        </is>
-      </c>
-      <c r="O46" s="15" t="inlineStr">
-        <is>
-          <t>Poça negra infinitamente profunda</t>
+      <c r="K46" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L46" s="19" t="inlineStr"/>
+      <c r="M46" s="19" t="inlineStr">
+        <is>
+          <t>Fire+Wind+Earth+Lightning</t>
+        </is>
+      </c>
+      <c r="N46" s="19" t="inlineStr">
+        <is>
+          <t>Apocalipse elemental. Earthquake + firestorm + lightning.</t>
+        </is>
+      </c>
+      <c r="O46" s="19" t="inlineStr">
+        <is>
+          <t>Terra rachando com lava e raios</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>VoidCurrent</t>
-        </is>
-      </c>
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>OFF_VoidCurrent</t>
-        </is>
-      </c>
-      <c r="C47" s="15" t="inlineStr">
-        <is>
-          <t>Corrente do Vazio</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="E47" s="15" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="inlineStr">
-        <is>
-          <t>Beam</t>
-        </is>
-      </c>
-      <c r="G47" s="15" t="inlineStr"/>
-      <c r="H47" s="15" t="inlineStr"/>
-      <c r="I47" s="16" t="n">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>EntropyCascade</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>OFF_EntropyCascade</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>Cascata Entrópica</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>Supreme</t>
+        </is>
+      </c>
+      <c r="F47" s="19" t="inlineStr">
+        <is>
+          <t>AoE</t>
+        </is>
+      </c>
+      <c r="G47" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="J47" s="15" t="inlineStr"/>
-      <c r="K47" s="16" t="n">
+      <c r="H47" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="L47" s="16" t="n">
+      <c r="I47" s="19" t="inlineStr"/>
+      <c r="J47" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="M47" s="15" t="inlineStr">
-        <is>
-          <t>Water+Lightning+Reality</t>
-        </is>
-      </c>
-      <c r="N47" s="15" t="inlineStr">
-        <is>
-          <t>Raio aquático corrompido. Chain + debuff.</t>
-        </is>
-      </c>
-      <c r="O47" s="15" t="inlineStr">
-        <is>
-          <t>Raio azul-púrpura fluido</t>
+      <c r="K47" s="19" t="inlineStr"/>
+      <c r="L47" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M47" s="19" t="inlineStr">
+        <is>
+          <t>Fire+Wind+Earth+Reality</t>
+        </is>
+      </c>
+      <c r="N47" s="19" t="inlineStr">
+        <is>
+          <t>Realidade se desintegra. Fragmentos causam dano misto.</t>
+        </is>
+      </c>
+      <c r="O47" s="19" t="inlineStr">
+        <is>
+          <t>Pedaços de realidade flutuando</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>DimAnchor</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>OFF_DimAnchor</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="inlineStr">
-        <is>
-          <t>Âncora Dimensional</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="F48" s="15" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>Annihilation</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>OFF_Annihilation</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>Aniquilação</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>Supreme</t>
+        </is>
+      </c>
+      <c r="F48" s="19" t="inlineStr">
+        <is>
+          <t>Orb</t>
+        </is>
+      </c>
+      <c r="G48" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H48" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I48" s="19" t="inlineStr"/>
+      <c r="J48" s="19" t="inlineStr"/>
+      <c r="K48" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L48" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M48" s="19" t="inlineStr">
+        <is>
+          <t>Fire+Wind+Lightning+Reality</t>
+        </is>
+      </c>
+      <c r="N48" s="19" t="inlineStr">
+        <is>
+          <t>Projétil → singularidade: puxa 8m → explode.</t>
+        </is>
+      </c>
+      <c r="O48" s="19" t="inlineStr">
+        <is>
+          <t>Esfera colapsando em si</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>Krakatoa</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>OFF_Krakatoa</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>Krakatoa</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>Supreme</t>
+        </is>
+      </c>
+      <c r="F49" s="19" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G48" s="15" t="inlineStr"/>
-      <c r="H48" s="15" t="inlineStr"/>
-      <c r="I48" s="15" t="inlineStr"/>
-      <c r="J48" s="16" t="n">
+      <c r="G49" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="K48" s="16" t="n">
+      <c r="H49" s="19" t="inlineStr"/>
+      <c r="I49" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="L48" s="16" t="n">
+      <c r="J49" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="M48" s="15" t="inlineStr">
-        <is>
-          <t>Earth+Lightning+Reality</t>
-        </is>
-      </c>
-      <c r="N48" s="15" t="inlineStr">
-        <is>
-          <t>Fixa inimigos na dimensão. Root + dmg exótico.</t>
-        </is>
-      </c>
-      <c r="O48" s="15" t="inlineStr">
-        <is>
-          <t>Correntes de energia no chão</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="17" t="inlineStr">
-        <is>
-          <t>Inferno_Ult</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>OFF_Inferno_Ult</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>Inferno Supremo</t>
-        </is>
-      </c>
-      <c r="D49" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="E49" s="17" t="inlineStr">
-        <is>
-          <t>Ultimate</t>
-        </is>
-      </c>
-      <c r="F49" s="17" t="inlineStr">
+      <c r="K49" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L49" s="19" t="inlineStr"/>
+      <c r="M49" s="19" t="inlineStr">
+        <is>
+          <t>Fire+Water+Earth+Lightning</t>
+        </is>
+      </c>
+      <c r="N49" s="19" t="inlineStr">
+        <is>
+          <t>Erupção oceânica. Tsunami de lava + raios.</t>
+        </is>
+      </c>
+      <c r="O49" s="19" t="inlineStr">
+        <is>
+          <t>Vulcão submarino com ondas</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>Genesis</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>OFF_Genesis</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>Gênesis Entrópica</t>
+        </is>
+      </c>
+      <c r="D50" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>Supreme</t>
+        </is>
+      </c>
+      <c r="F50" s="19" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G49" s="18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H49" s="17" t="inlineStr"/>
-      <c r="I49" s="17" t="inlineStr"/>
-      <c r="J49" s="17" t="inlineStr"/>
-      <c r="K49" s="17" t="inlineStr"/>
-      <c r="L49" s="17" t="inlineStr"/>
-      <c r="M49" s="17" t="inlineStr">
-        <is>
-          <t>Fire×3</t>
-        </is>
-      </c>
-      <c r="N49" s="17" t="inlineStr">
-        <is>
-          <t>Área 50% maior. Trail de fogo por 3s.</t>
-        </is>
-      </c>
-      <c r="O49" s="17" t="inlineStr">
-        <is>
-          <t>Mar de chamas expandindo</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t>Volcano_Ult</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>OFF_Volcano_Ult</t>
-        </is>
-      </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>Vulcão</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="n">
-        <v>41</v>
-      </c>
-      <c r="E50" s="17" t="inlineStr">
-        <is>
-          <t>Ultimate</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
+      <c r="G50" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H50" s="19" t="inlineStr"/>
+      <c r="I50" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J50" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K50" s="19" t="inlineStr"/>
+      <c r="L50" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M50" s="19" t="inlineStr">
+        <is>
+          <t>Fire+Water+Earth+Reality</t>
+        </is>
+      </c>
+      <c r="N50" s="19" t="inlineStr">
+        <is>
+          <t>Zona de caos primordial. Efeitos random por tick.</t>
+        </is>
+      </c>
+      <c r="O50" s="19" t="inlineStr">
+        <is>
+          <t>Zona de cores impossíveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>VoidMaelstrom</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>OFF_VoidMaelstrom</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>Vórtice do Vazio</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>Supreme</t>
+        </is>
+      </c>
+      <c r="F51" s="19" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G50" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H50" s="17" t="inlineStr"/>
-      <c r="I50" s="17" t="inlineStr"/>
-      <c r="J50" s="18" t="n">
+      <c r="G51" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="K50" s="17" t="inlineStr"/>
-      <c r="L50" s="17" t="inlineStr"/>
-      <c r="M50" s="17" t="inlineStr">
-        <is>
-          <t>Fire×2+Earth</t>
-        </is>
-      </c>
-      <c r="N50" s="17" t="inlineStr">
-        <is>
-          <t>Pool que CRESCE por 5s. Centro faz mais dano.</t>
-        </is>
-      </c>
-      <c r="O50" s="17" t="inlineStr">
-        <is>
-          <t>Caldeira de lava expandindo</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="17" t="inlineStr">
-        <is>
-          <t>Pyroclasm_Ult</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>OFF_Pyroclasm_Ult</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>Cataclisma</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="n">
-        <v>42</v>
-      </c>
-      <c r="E51" s="17" t="inlineStr">
-        <is>
-          <t>Ultimate</t>
-        </is>
-      </c>
-      <c r="F51" s="17" t="inlineStr">
+      <c r="H51" s="19" t="inlineStr"/>
+      <c r="I51" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J51" s="19" t="inlineStr"/>
+      <c r="K51" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L51" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M51" s="19" t="inlineStr">
+        <is>
+          <t>Fire+Water+Lightning+Reality</t>
+        </is>
+      </c>
+      <c r="N51" s="19" t="inlineStr">
+        <is>
+          <t>Maelstrom corrompido. Drain HP + mana de inimigos.</t>
+        </is>
+      </c>
+      <c r="O51" s="19" t="inlineStr">
+        <is>
+          <t>Vórtice aquático púrpura com raios</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>NeutronStar</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>OFF_NeutronStar</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>Estrela de Nêutrons</t>
+        </is>
+      </c>
+      <c r="D52" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>Supreme</t>
+        </is>
+      </c>
+      <c r="F52" s="19" t="inlineStr">
+        <is>
+          <t>Orb</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H52" s="19" t="inlineStr"/>
+      <c r="I52" s="19" t="inlineStr"/>
+      <c r="J52" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K52" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L52" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M52" s="19" t="inlineStr">
+        <is>
+          <t>Fire+Earth+Lightning+Reality</t>
+        </is>
+      </c>
+      <c r="N52" s="19" t="inlineStr">
+        <is>
+          <t>Massa ultra-densa. Impacto → micro-singularidade.</t>
+        </is>
+      </c>
+      <c r="O52" s="19" t="inlineStr">
+        <is>
+          <t>Esfera super-brilhante minúscula</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>Leviathan</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>OFF_Leviathan</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>Leviatã</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>Supreme</t>
+        </is>
+      </c>
+      <c r="F53" s="19" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G51" s="18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H51" s="18" t="n">
+      <c r="G53" s="19" t="inlineStr"/>
+      <c r="H53" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="I51" s="17" t="inlineStr"/>
-      <c r="J51" s="18" t="n">
+      <c r="I53" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="K51" s="17" t="inlineStr"/>
-      <c r="L51" s="17" t="inlineStr"/>
-      <c r="M51" s="17" t="inlineStr">
-        <is>
-          <t>Fire+Fire+Wind+Earth</t>
-        </is>
-      </c>
-      <c r="N51" s="17" t="inlineStr">
-        <is>
-          <t>Rochas em 3 ondas. Cada onda empurra mais.</t>
-        </is>
-      </c>
-      <c r="O51" s="17" t="inlineStr">
-        <is>
-          <t>Chuva de meteoros</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="17" t="inlineStr">
-        <is>
-          <t>Plasma_Ult</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>OFF_Plasma_Ult</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>Coluna de Plasma</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="n">
-        <v>41</v>
-      </c>
-      <c r="E52" s="17" t="inlineStr">
-        <is>
-          <t>Ultimate</t>
-        </is>
-      </c>
-      <c r="F52" s="17" t="inlineStr">
-        <is>
-          <t>Beam</t>
-        </is>
-      </c>
-      <c r="G52" s="18" t="n">
+      <c r="J53" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="H52" s="17" t="inlineStr"/>
-      <c r="I52" s="17" t="inlineStr"/>
-      <c r="J52" s="17" t="inlineStr"/>
-      <c r="K52" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L52" s="17" t="inlineStr"/>
-      <c r="M52" s="17" t="inlineStr">
-        <is>
-          <t>Lightning×2+Fire</t>
-        </is>
-      </c>
-      <c r="N52" s="17" t="inlineStr">
-        <is>
-          <t>Perfura terreno. Ignora cobertura. +15% crit.</t>
-        </is>
-      </c>
-      <c r="O52" s="17" t="inlineStr">
-        <is>
-          <t>Coluna branca incandescente</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="17" t="inlineStr">
-        <is>
-          <t>ChainLightning_Ult</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>OFF_ChainLightning_Ult</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>Tempestade Arcana</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="n">
-        <v>42</v>
-      </c>
-      <c r="E53" s="17" t="inlineStr">
-        <is>
-          <t>Ultimate</t>
-        </is>
-      </c>
-      <c r="F53" s="17" t="inlineStr">
-        <is>
-          <t>Beam</t>
-        </is>
-      </c>
-      <c r="G53" s="17" t="inlineStr"/>
-      <c r="H53" s="18" t="n">
+      <c r="K53" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="I53" s="17" t="inlineStr"/>
-      <c r="J53" s="17" t="inlineStr"/>
-      <c r="K53" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L53" s="17" t="inlineStr"/>
-      <c r="M53" s="17" t="inlineStr">
-        <is>
-          <t>Lightning×2+Wind</t>
-        </is>
-      </c>
-      <c r="N53" s="17" t="inlineStr">
-        <is>
-          <t>Pula 5 alvos. Dano não diminui por salto.</t>
-        </is>
-      </c>
-      <c r="O53" s="17" t="inlineStr">
-        <is>
-          <t>Teia de raios</t>
+      <c r="L53" s="19" t="inlineStr"/>
+      <c r="M53" s="19" t="inlineStr">
+        <is>
+          <t>Wind+Water+Earth+Lightning</t>
+        </is>
+      </c>
+      <c r="N53" s="19" t="inlineStr">
+        <is>
+          <t>Monstro elemental. Ondas + terremoto + raios.</t>
+        </is>
+      </c>
+      <c r="O53" s="19" t="inlineStr">
+        <is>
+          <t>Forma serpentina de água e terra</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="inlineStr">
-        <is>
-          <t>Blizzard_Ult</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>OFF_Blizzard_Ult</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>Era Glacial</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="n">
-        <v>41</v>
-      </c>
-      <c r="E54" s="17" t="inlineStr">
-        <is>
-          <t>Ultimate</t>
-        </is>
-      </c>
-      <c r="F54" s="17" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>WorldEater</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>OFF_WorldEater</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>Devorador de Mundos</t>
+        </is>
+      </c>
+      <c r="D54" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>Supreme</t>
+        </is>
+      </c>
+      <c r="F54" s="19" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G54" s="17" t="inlineStr"/>
-      <c r="H54" s="18" t="n">
+      <c r="G54" s="19" t="inlineStr"/>
+      <c r="H54" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="I54" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J54" s="17" t="inlineStr"/>
-      <c r="K54" s="17" t="inlineStr"/>
-      <c r="L54" s="17" t="inlineStr"/>
-      <c r="M54" s="17" t="inlineStr">
-        <is>
-          <t>Water×2+Wind</t>
-        </is>
-      </c>
-      <c r="N54" s="17" t="inlineStr">
-        <is>
-          <t>Freeze garantido. Área cresce ao longo de 4s.</t>
-        </is>
-      </c>
-      <c r="O54" s="17" t="inlineStr">
-        <is>
-          <t>Expansão de gelo cristalino</t>
+      <c r="I54" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J54" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K54" s="19" t="inlineStr"/>
+      <c r="L54" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M54" s="19" t="inlineStr">
+        <is>
+          <t>Wind+Water+Earth+Reality</t>
+        </is>
+      </c>
+      <c r="N54" s="19" t="inlineStr">
+        <is>
+          <t>Buraco negro natural. Puxa + crush + void dmg.</t>
+        </is>
+      </c>
+      <c r="O54" s="19" t="inlineStr">
+        <is>
+          <t>Esfera de destruição natural</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="inlineStr">
-        <is>
-          <t>Petrify_Ult</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>OFF_Petrify_Ult</t>
-        </is>
-      </c>
-      <c r="C55" s="17" t="inlineStr">
-        <is>
-          <t>Medusa</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="n">
-        <v>41</v>
-      </c>
-      <c r="E55" s="17" t="inlineStr">
-        <is>
-          <t>Ultimate</t>
-        </is>
-      </c>
-      <c r="F55" s="17" t="inlineStr">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>AbsoluteZero</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>OFF_AbsoluteZero</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="inlineStr">
+        <is>
+          <t>Zero Absoluto</t>
+        </is>
+      </c>
+      <c r="D55" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t>Supreme</t>
+        </is>
+      </c>
+      <c r="F55" s="19" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G55" s="17" t="inlineStr"/>
-      <c r="H55" s="17" t="inlineStr"/>
-      <c r="I55" s="17" t="inlineStr"/>
-      <c r="J55" s="18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K55" s="17" t="inlineStr"/>
-      <c r="L55" s="18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M55" s="17" t="inlineStr">
-        <is>
-          <t>Earth×2+Reality / Earth+Reality×2</t>
-        </is>
-      </c>
-      <c r="N55" s="17" t="inlineStr">
-        <is>
-          <t>Cone: petrifica múltiplos. Explodem ao tomar dano.</t>
-        </is>
-      </c>
-      <c r="O55" s="17" t="inlineStr">
-        <is>
-          <t>Onda cinza petrificante</t>
+      <c r="G55" s="19" t="inlineStr"/>
+      <c r="H55" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I55" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J55" s="19" t="inlineStr"/>
+      <c r="K55" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L55" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M55" s="19" t="inlineStr">
+        <is>
+          <t>Wind+Water+Lightning+Reality</t>
+        </is>
+      </c>
+      <c r="N55" s="19" t="inlineStr">
+        <is>
+          <t>Congela até a realidade. Shatter: 3× dano.</t>
+        </is>
+      </c>
+      <c r="O55" s="19" t="inlineStr">
+        <is>
+          <t>Expansão de gelo cósmico</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="19" t="inlineStr">
         <is>
-          <t>PrimordialTempest</t>
+          <t>DimCollapse</t>
         </is>
       </c>
       <c r="B56" s="19" t="inlineStr">
         <is>
-          <t>OFF_PrimordialTempest</t>
+          <t>OFF_DimCollapse</t>
         </is>
       </c>
       <c r="C56" s="19" t="inlineStr">
         <is>
-          <t>Tempestade Primordial</t>
+          <t>Colapso Dimensional</t>
         </is>
       </c>
       <c r="D56" s="19" t="n">
@@ -4580,50 +4690,50 @@
           <t>AoE</t>
         </is>
       </c>
-      <c r="G56" s="20" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="G56" s="19" t="inlineStr"/>
       <c r="H56" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="I56" s="20" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="I56" s="19" t="inlineStr"/>
       <c r="J56" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="K56" s="19" t="inlineStr"/>
-      <c r="L56" s="19" t="inlineStr"/>
+      <c r="K56" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L56" s="20" t="n">
+        <v>0.8</v>
+      </c>
       <c r="M56" s="19" t="inlineStr">
         <is>
-          <t>Fire+Wind+Water+Earth</t>
+          <t>Wind+Earth+Lightning+Reality</t>
         </is>
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Os 4 elementos naturais. Caos total: fogo+gelo+vento+terra.</t>
+          <t>Dimensão implode. AoE + stun + void DoT.</t>
         </is>
       </c>
       <c r="O56" s="19" t="inlineStr">
         <is>
-          <t>Vórtice com 4 elementos visíveis</t>
+          <t>Espaço dobrando sobre si mesmo</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="19" t="inlineStr">
         <is>
-          <t>TyphoonInfernal</t>
+          <t>EventHorizon</t>
         </is>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t>OFF_TyphoonInfernal</t>
+          <t>OFF_EventHorizon</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t>Tufão Infernal</t>
+          <t>Horizonte de Eventos</t>
         </is>
       </c>
       <c r="D57" s="19" t="n">
@@ -4639,1085 +4749,456 @@
           <t>AoE</t>
         </is>
       </c>
-      <c r="G57" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H57" s="20" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="G57" s="19" t="inlineStr"/>
+      <c r="H57" s="19" t="inlineStr"/>
       <c r="I57" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="J57" s="19" t="inlineStr"/>
+      <c r="J57" s="20" t="n">
+        <v>0.8</v>
+      </c>
       <c r="K57" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="L57" s="19" t="inlineStr"/>
+      <c r="L57" s="20" t="n">
+        <v>0.8</v>
+      </c>
       <c r="M57" s="19" t="inlineStr">
         <is>
-          <t>Fire+Wind+Water+Lightning</t>
+          <t>Water+Earth+Lightning+Reality</t>
         </is>
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Mega-tempestade flamejante. Burn+Slow+Stun rotativos.</t>
+          <t>Singularidade aquática. Nada escapa. Pull + dano.</t>
         </is>
       </c>
       <c r="O57" s="19" t="inlineStr">
         <is>
-          <t>Furacão de fogo com raios</t>
+          <t>Esfera negra com anel de acreção</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="19" t="inlineStr">
-        <is>
-          <t>ElementalRift</t>
-        </is>
-      </c>
-      <c r="B58" s="19" t="inlineStr">
-        <is>
-          <t>OFF_ElementalRift</t>
-        </is>
-      </c>
-      <c r="C58" s="19" t="inlineStr">
-        <is>
-          <t>Fenda Elemental</t>
-        </is>
-      </c>
-      <c r="D58" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="E58" s="19" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PrimalApocalypse</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>OFF_PrimalApocalypse</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Apocalipse Primordial</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>60</v>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>Supreme</t>
         </is>
       </c>
-      <c r="F58" s="19" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G58" s="20" t="n">
+      <c r="G58" t="n">
         <v>0.8</v>
       </c>
-      <c r="H58" s="20" t="n">
+      <c r="H58" t="n">
         <v>0.8</v>
       </c>
-      <c r="I58" s="20" t="n">
+      <c r="I58" t="n">
         <v>0.8</v>
       </c>
-      <c r="J58" s="19" t="inlineStr"/>
-      <c r="K58" s="19" t="inlineStr"/>
-      <c r="L58" s="20" t="n">
+      <c r="J58" t="n">
         <v>0.8</v>
       </c>
-      <c r="M58" s="19" t="inlineStr">
-        <is>
-          <t>Fire+Wind+Water+Reality</t>
-        </is>
-      </c>
-      <c r="N58" s="19" t="inlineStr">
-        <is>
-          <t>Fenda na realidade. Elementos brotam caoticamente.</t>
-        </is>
-      </c>
-      <c r="O58" s="19" t="inlineStr">
-        <is>
-          <t>Rasgo no ar com água, fogo e vento</t>
+      <c r="K58" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Fire, Wind, Water, Earth, Lightning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Convergência dos cinco elementos fundamentais. Devastação absoluta em área.</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Explosão multicolorida com ondas de choque</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="19" t="inlineStr">
-        <is>
-          <t>Ragnarok</t>
-        </is>
-      </c>
-      <c r="B59" s="19" t="inlineStr">
-        <is>
-          <t>OFF_Ragnarok</t>
-        </is>
-      </c>
-      <c r="C59" s="19" t="inlineStr">
-        <is>
-          <t>Ragnarök</t>
-        </is>
-      </c>
-      <c r="D59" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="E59" s="19" t="inlineStr">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CosmicErosion</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>OFF_CosmicErosion</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Erosão Cósmica</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>60</v>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>Supreme</t>
         </is>
       </c>
-      <c r="F59" s="19" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G59" s="20" t="n">
+      <c r="G59" t="n">
         <v>0.8</v>
       </c>
-      <c r="H59" s="20" t="n">
+      <c r="H59" t="n">
         <v>0.8</v>
       </c>
-      <c r="I59" s="19" t="inlineStr"/>
-      <c r="J59" s="20" t="n">
+      <c r="I59" t="n">
         <v>0.8</v>
       </c>
-      <c r="K59" s="20" t="n">
+      <c r="J59" t="n">
         <v>0.8</v>
       </c>
-      <c r="L59" s="19" t="inlineStr"/>
-      <c r="M59" s="19" t="inlineStr">
-        <is>
-          <t>Fire+Wind+Earth+Lightning</t>
-        </is>
-      </c>
-      <c r="N59" s="19" t="inlineStr">
-        <is>
-          <t>Apocalipse elemental. Earthquake + firestorm + lightning.</t>
-        </is>
-      </c>
-      <c r="O59" s="19" t="inlineStr">
-        <is>
-          <t>Terra rachando com lava e raios</t>
+      <c r="L59" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Fire, Wind, Water, Earth, Reality</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>A realidade se dissolve sob pressão elemental massiva. Dano contínuo.</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Fissuras de luz no chão com partículas de todos os elementos</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="19" t="inlineStr">
-        <is>
-          <t>EntropyCascade</t>
-        </is>
-      </c>
-      <c r="B60" s="19" t="inlineStr">
-        <is>
-          <t>OFF_EntropyCascade</t>
-        </is>
-      </c>
-      <c r="C60" s="19" t="inlineStr">
-        <is>
-          <t>Cascata Entrópica</t>
-        </is>
-      </c>
-      <c r="D60" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="E60" s="19" t="inlineStr">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>EtherealTempest</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>OFF_EtherealTempest</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Tempestade Etérea</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>60</v>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>Supreme</t>
         </is>
       </c>
-      <c r="F60" s="19" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G60" s="20" t="n">
+      <c r="G60" t="n">
         <v>0.8</v>
       </c>
-      <c r="H60" s="20" t="n">
+      <c r="H60" t="n">
         <v>0.8</v>
       </c>
-      <c r="I60" s="19" t="inlineStr"/>
-      <c r="J60" s="20" t="n">
+      <c r="I60" t="n">
         <v>0.8</v>
       </c>
-      <c r="K60" s="19" t="inlineStr"/>
-      <c r="L60" s="20" t="n">
+      <c r="K60" t="n">
         <v>0.8</v>
       </c>
-      <c r="M60" s="19" t="inlineStr">
-        <is>
-          <t>Fire+Wind+Earth+Reality</t>
-        </is>
-      </c>
-      <c r="N60" s="19" t="inlineStr">
-        <is>
-          <t>Realidade se desintegra. Fragmentos causam dano misto.</t>
-        </is>
-      </c>
-      <c r="O60" s="19" t="inlineStr">
-        <is>
-          <t>Pedaços de realidade flutuando</t>
+      <c r="L60" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Fire, Wind, Water, Lightning, Reality</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Tempestade de energia pura sem ancoragem física. Caos etéreo.</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Vórtice translúcido com relâmpagos e distorção</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="19" t="inlineStr">
-        <is>
-          <t>Annihilation</t>
-        </is>
-      </c>
-      <c r="B61" s="19" t="inlineStr">
-        <is>
-          <t>OFF_Annihilation</t>
-        </is>
-      </c>
-      <c r="C61" s="19" t="inlineStr">
-        <is>
-          <t>Aniquilação</t>
-        </is>
-      </c>
-      <c r="D61" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="E61" s="19" t="inlineStr">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PlanetarySunder</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>OFF_PlanetarySunder</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Fragmentação Planetária</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>60</v>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>Supreme</t>
         </is>
       </c>
-      <c r="F61" s="19" t="inlineStr">
-        <is>
-          <t>Orb</t>
-        </is>
-      </c>
-      <c r="G61" s="20" t="n">
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>AoE</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
         <v>0.8</v>
       </c>
-      <c r="H61" s="20" t="n">
+      <c r="H61" t="n">
         <v>0.8</v>
       </c>
-      <c r="I61" s="19" t="inlineStr"/>
-      <c r="J61" s="19" t="inlineStr"/>
-      <c r="K61" s="20" t="n">
+      <c r="J61" t="n">
         <v>0.8</v>
       </c>
-      <c r="L61" s="20" t="n">
+      <c r="K61" t="n">
         <v>0.8</v>
       </c>
-      <c r="M61" s="19" t="inlineStr">
-        <is>
-          <t>Fire+Wind+Lightning+Reality</t>
-        </is>
-      </c>
-      <c r="N61" s="19" t="inlineStr">
-        <is>
-          <t>Projétil → singularidade: puxa 8m → explode.</t>
-        </is>
-      </c>
-      <c r="O61" s="19" t="inlineStr">
-        <is>
-          <t>Esfera colapsando em si</t>
+      <c r="L61" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Fire, Wind, Earth, Lightning, Reality</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Fratura sísmica amplificada por todas as forças destrutivas.</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Chão rachando com magma, raios e distorções dimensionais</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="19" t="inlineStr">
-        <is>
-          <t>Krakatoa</t>
-        </is>
-      </c>
-      <c r="B62" s="19" t="inlineStr">
-        <is>
-          <t>OFF_Krakatoa</t>
-        </is>
-      </c>
-      <c r="C62" s="19" t="inlineStr">
-        <is>
-          <t>Krakatoa</t>
-        </is>
-      </c>
-      <c r="D62" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="E62" s="19" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ChaosTide</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>OFF_ChaosTide</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Maré do Caos</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>60</v>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>Supreme</t>
         </is>
       </c>
-      <c r="F62" s="19" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G62" s="20" t="n">
+      <c r="G62" t="n">
         <v>0.8</v>
       </c>
-      <c r="H62" s="19" t="inlineStr"/>
-      <c r="I62" s="20" t="n">
+      <c r="I62" t="n">
         <v>0.8</v>
       </c>
-      <c r="J62" s="20" t="n">
+      <c r="J62" t="n">
         <v>0.8</v>
       </c>
-      <c r="K62" s="20" t="n">
+      <c r="K62" t="n">
         <v>0.8</v>
       </c>
-      <c r="L62" s="19" t="inlineStr"/>
-      <c r="M62" s="19" t="inlineStr">
-        <is>
-          <t>Fire+Water+Earth+Lightning</t>
-        </is>
-      </c>
-      <c r="N62" s="19" t="inlineStr">
-        <is>
-          <t>Erupção oceânica. Tsunami de lava + raios.</t>
-        </is>
-      </c>
-      <c r="O62" s="19" t="inlineStr">
-        <is>
-          <t>Vulcão submarino com ondas</t>
+      <c r="L62" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Fire, Water, Earth, Lightning, Reality</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Onda avassaladora que distorce matéria e energia.</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Tsunami de lava eletrificada com distorção dimensional</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="19" t="inlineStr">
-        <is>
-          <t>Genesis</t>
-        </is>
-      </c>
-      <c r="B63" s="19" t="inlineStr">
-        <is>
-          <t>OFF_Genesis</t>
-        </is>
-      </c>
-      <c r="C63" s="19" t="inlineStr">
-        <is>
-          <t>Gênesis Entrópica</t>
-        </is>
-      </c>
-      <c r="D63" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="E63" s="19" t="inlineStr">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>GlacialObliteration</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>OFF_GlacialObliteration</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Obliteração Glacial</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>60</v>
+      </c>
+      <c r="E63" t="inlineStr">
         <is>
           <t>Supreme</t>
         </is>
       </c>
-      <c r="F63" s="19" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G63" s="20" t="n">
+      <c r="H63" t="n">
         <v>0.8</v>
       </c>
-      <c r="H63" s="19" t="inlineStr"/>
-      <c r="I63" s="20" t="n">
+      <c r="I63" t="n">
         <v>0.8</v>
       </c>
-      <c r="J63" s="20" t="n">
+      <c r="J63" t="n">
         <v>0.8</v>
       </c>
-      <c r="K63" s="19" t="inlineStr"/>
-      <c r="L63" s="20" t="n">
+      <c r="K63" t="n">
         <v>0.8</v>
       </c>
-      <c r="M63" s="19" t="inlineStr">
-        <is>
-          <t>Fire+Water+Earth+Reality</t>
-        </is>
-      </c>
-      <c r="N63" s="19" t="inlineStr">
-        <is>
-          <t>Zona de caos primordial. Efeitos random por tick.</t>
-        </is>
-      </c>
-      <c r="O63" s="19" t="inlineStr">
-        <is>
-          <t>Zona de cores impossíveis</t>
+      <c r="L63" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Wind, Water, Earth, Lightning, Reality</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Aniquilação gelada absoluta. Tudo congela e se desfaz.</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Onda de gelo cristalino com relâmpagos e fissuras dimensionais</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="19" t="inlineStr">
-        <is>
-          <t>VoidMaelstrom</t>
-        </is>
-      </c>
-      <c r="B64" s="19" t="inlineStr">
-        <is>
-          <t>OFF_VoidMaelstrom</t>
-        </is>
-      </c>
-      <c r="C64" s="19" t="inlineStr">
-        <is>
-          <t>Vórtice do Vazio</t>
-        </is>
-      </c>
-      <c r="D64" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="E64" s="19" t="inlineStr">
-        <is>
-          <t>Supreme</t>
-        </is>
-      </c>
-      <c r="F64" s="19" t="inlineStr">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BigBang</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>OFF_BigBang</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Big Bang</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>70</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Ultimate</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>AoE</t>
         </is>
       </c>
-      <c r="G64" s="20" t="n">
+      <c r="G64" t="n">
         <v>0.8</v>
       </c>
-      <c r="H64" s="19" t="inlineStr"/>
-      <c r="I64" s="20" t="n">
+      <c r="H64" t="n">
         <v>0.8</v>
       </c>
-      <c r="J64" s="19" t="inlineStr"/>
-      <c r="K64" s="20" t="n">
+      <c r="I64" t="n">
         <v>0.8</v>
       </c>
-      <c r="L64" s="20" t="n">
+      <c r="J64" t="n">
         <v>0.8</v>
       </c>
-      <c r="M64" s="19" t="inlineStr">
-        <is>
-          <t>Fire+Water+Lightning+Reality</t>
-        </is>
-      </c>
-      <c r="N64" s="19" t="inlineStr">
-        <is>
-          <t>Maelstrom corrompido. Drain HP + mana de inimigos.</t>
-        </is>
-      </c>
-      <c r="O64" s="19" t="inlineStr">
-        <is>
-          <t>Vórtice aquático púrpura com raios</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="19" t="inlineStr">
-        <is>
-          <t>NeutronStar</t>
-        </is>
-      </c>
-      <c r="B65" s="19" t="inlineStr">
-        <is>
-          <t>OFF_NeutronStar</t>
-        </is>
-      </c>
-      <c r="C65" s="19" t="inlineStr">
-        <is>
-          <t>Estrela de Nêutrons</t>
-        </is>
-      </c>
-      <c r="D65" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="E65" s="19" t="inlineStr">
-        <is>
-          <t>Supreme</t>
-        </is>
-      </c>
-      <c r="F65" s="19" t="inlineStr">
-        <is>
-          <t>Orb</t>
-        </is>
-      </c>
-      <c r="G65" s="20" t="n">
+      <c r="K64" t="n">
         <v>0.8</v>
       </c>
-      <c r="H65" s="19" t="inlineStr"/>
-      <c r="I65" s="19" t="inlineStr"/>
-      <c r="J65" s="20" t="n">
+      <c r="L64" t="n">
         <v>0.8</v>
       </c>
-      <c r="K65" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L65" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M65" s="19" t="inlineStr">
-        <is>
-          <t>Fire+Earth+Lightning+Reality</t>
-        </is>
-      </c>
-      <c r="N65" s="19" t="inlineStr">
-        <is>
-          <t>Massa ultra-densa. Impacto → micro-singularidade.</t>
-        </is>
-      </c>
-      <c r="O65" s="19" t="inlineStr">
-        <is>
-          <t>Esfera super-brilhante minúscula</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="19" t="inlineStr">
-        <is>
-          <t>Leviathan</t>
-        </is>
-      </c>
-      <c r="B66" s="19" t="inlineStr">
-        <is>
-          <t>OFF_Leviathan</t>
-        </is>
-      </c>
-      <c r="C66" s="19" t="inlineStr">
-        <is>
-          <t>Leviatã</t>
-        </is>
-      </c>
-      <c r="D66" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="E66" s="19" t="inlineStr">
-        <is>
-          <t>Supreme</t>
-        </is>
-      </c>
-      <c r="F66" s="19" t="inlineStr">
-        <is>
-          <t>AoE</t>
-        </is>
-      </c>
-      <c r="G66" s="19" t="inlineStr"/>
-      <c r="H66" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I66" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J66" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K66" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L66" s="19" t="inlineStr"/>
-      <c r="M66" s="19" t="inlineStr">
-        <is>
-          <t>Wind+Water+Earth+Lightning</t>
-        </is>
-      </c>
-      <c r="N66" s="19" t="inlineStr">
-        <is>
-          <t>Monstro elemental. Ondas + terremoto + raios.</t>
-        </is>
-      </c>
-      <c r="O66" s="19" t="inlineStr">
-        <is>
-          <t>Forma serpentina de água e terra</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="19" t="inlineStr">
-        <is>
-          <t>WorldEater</t>
-        </is>
-      </c>
-      <c r="B67" s="19" t="inlineStr">
-        <is>
-          <t>OFF_WorldEater</t>
-        </is>
-      </c>
-      <c r="C67" s="19" t="inlineStr">
-        <is>
-          <t>Devorador de Mundos</t>
-        </is>
-      </c>
-      <c r="D67" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="E67" s="19" t="inlineStr">
-        <is>
-          <t>Supreme</t>
-        </is>
-      </c>
-      <c r="F67" s="19" t="inlineStr">
-        <is>
-          <t>AoE</t>
-        </is>
-      </c>
-      <c r="G67" s="19" t="inlineStr"/>
-      <c r="H67" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I67" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J67" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K67" s="19" t="inlineStr"/>
-      <c r="L67" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M67" s="19" t="inlineStr">
-        <is>
-          <t>Wind+Water+Earth+Reality</t>
-        </is>
-      </c>
-      <c r="N67" s="19" t="inlineStr">
-        <is>
-          <t>Buraco negro natural. Puxa + crush + void dmg.</t>
-        </is>
-      </c>
-      <c r="O67" s="19" t="inlineStr">
-        <is>
-          <t>Esfera de destruição natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="19" t="inlineStr">
-        <is>
-          <t>AbsoluteZero</t>
-        </is>
-      </c>
-      <c r="B68" s="19" t="inlineStr">
-        <is>
-          <t>OFF_AbsoluteZero</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>Zero Absoluto</t>
-        </is>
-      </c>
-      <c r="D68" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="E68" s="19" t="inlineStr">
-        <is>
-          <t>Supreme</t>
-        </is>
-      </c>
-      <c r="F68" s="19" t="inlineStr">
-        <is>
-          <t>AoE</t>
-        </is>
-      </c>
-      <c r="G68" s="19" t="inlineStr"/>
-      <c r="H68" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I68" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J68" s="19" t="inlineStr"/>
-      <c r="K68" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L68" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M68" s="19" t="inlineStr">
-        <is>
-          <t>Wind+Water+Lightning+Reality</t>
-        </is>
-      </c>
-      <c r="N68" s="19" t="inlineStr">
-        <is>
-          <t>Congela até a realidade. Shatter: 3× dano.</t>
-        </is>
-      </c>
-      <c r="O68" s="19" t="inlineStr">
-        <is>
-          <t>Expansão de gelo cósmico</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="19" t="inlineStr">
-        <is>
-          <t>DimCollapse</t>
-        </is>
-      </c>
-      <c r="B69" s="19" t="inlineStr">
-        <is>
-          <t>OFF_DimCollapse</t>
-        </is>
-      </c>
-      <c r="C69" s="19" t="inlineStr">
-        <is>
-          <t>Colapso Dimensional</t>
-        </is>
-      </c>
-      <c r="D69" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="E69" s="19" t="inlineStr">
-        <is>
-          <t>Supreme</t>
-        </is>
-      </c>
-      <c r="F69" s="19" t="inlineStr">
-        <is>
-          <t>AoE</t>
-        </is>
-      </c>
-      <c r="G69" s="19" t="inlineStr"/>
-      <c r="H69" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I69" s="19" t="inlineStr"/>
-      <c r="J69" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K69" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L69" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M69" s="19" t="inlineStr">
-        <is>
-          <t>Wind+Earth+Lightning+Reality</t>
-        </is>
-      </c>
-      <c r="N69" s="19" t="inlineStr">
-        <is>
-          <t>Dimensão implode. AoE + stun + void DoT.</t>
-        </is>
-      </c>
-      <c r="O69" s="19" t="inlineStr">
-        <is>
-          <t>Espaço dobrando sobre si mesmo</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="19" t="inlineStr">
-        <is>
-          <t>EventHorizon</t>
-        </is>
-      </c>
-      <c r="B70" s="19" t="inlineStr">
-        <is>
-          <t>OFF_EventHorizon</t>
-        </is>
-      </c>
-      <c r="C70" s="19" t="inlineStr">
-        <is>
-          <t>Horizonte de Eventos</t>
-        </is>
-      </c>
-      <c r="D70" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="E70" s="19" t="inlineStr">
-        <is>
-          <t>Supreme</t>
-        </is>
-      </c>
-      <c r="F70" s="19" t="inlineStr">
-        <is>
-          <t>AoE</t>
-        </is>
-      </c>
-      <c r="G70" s="19" t="inlineStr"/>
-      <c r="H70" s="19" t="inlineStr"/>
-      <c r="I70" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J70" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K70" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L70" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M70" s="19" t="inlineStr">
-        <is>
-          <t>Water+Earth+Lightning+Reality</t>
-        </is>
-      </c>
-      <c r="N70" s="19" t="inlineStr">
-        <is>
-          <t>Singularidade aquática. Nada escapa. Pull + dano.</t>
-        </is>
-      </c>
-      <c r="O70" s="19" t="inlineStr">
-        <is>
-          <t>Esfera negra com anel de acreção</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="21" t="inlineStr">
-        <is>
-          <t>Supernova</t>
-        </is>
-      </c>
-      <c r="B71" s="21" t="inlineStr">
-        <is>
-          <t>OFF_Supernova</t>
-        </is>
-      </c>
-      <c r="C71" s="21" t="inlineStr">
-        <is>
-          <t>Supernova</t>
-        </is>
-      </c>
-      <c r="D71" s="21" t="n">
-        <v>55</v>
-      </c>
-      <c r="E71" s="21" t="inlineStr">
-        <is>
-          <t>Supreme</t>
-        </is>
-      </c>
-      <c r="F71" s="21" t="inlineStr">
-        <is>
-          <t>AoE</t>
-        </is>
-      </c>
-      <c r="G71" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H71" s="22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I71" s="21" t="inlineStr"/>
-      <c r="J71" s="21" t="inlineStr"/>
-      <c r="K71" s="22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L71" s="21" t="inlineStr"/>
-      <c r="M71" s="21" t="inlineStr">
-        <is>
-          <t>Fire×2+Wind+Lightning</t>
-        </is>
-      </c>
-      <c r="N71" s="21" t="inlineStr">
-        <is>
-          <t>Explosão solar. AoE massiva + Burn + Blind.</t>
-        </is>
-      </c>
-      <c r="O71" s="21" t="inlineStr">
-        <is>
-          <t>Explosão branca ofuscante</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="21" t="inlineStr">
-        <is>
-          <t>WorldRend</t>
-        </is>
-      </c>
-      <c r="B72" s="21" t="inlineStr">
-        <is>
-          <t>OFF_WorldRend</t>
-        </is>
-      </c>
-      <c r="C72" s="21" t="inlineStr">
-        <is>
-          <t>Ruptura do Mundo</t>
-        </is>
-      </c>
-      <c r="D72" s="21" t="n">
-        <v>55</v>
-      </c>
-      <c r="E72" s="21" t="inlineStr">
-        <is>
-          <t>Supreme</t>
-        </is>
-      </c>
-      <c r="F72" s="21" t="inlineStr">
-        <is>
-          <t>AoE</t>
-        </is>
-      </c>
-      <c r="G72" s="21" t="inlineStr"/>
-      <c r="H72" s="22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I72" s="21" t="inlineStr"/>
-      <c r="J72" s="22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K72" s="21" t="inlineStr"/>
-      <c r="L72" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M72" s="21" t="inlineStr">
-        <is>
-          <t>Reality×2+Wind+Earth</t>
-        </is>
-      </c>
-      <c r="N72" s="21" t="inlineStr">
-        <is>
-          <t>Rasga realidade. Flutuam 2s → caem com dano.</t>
-        </is>
-      </c>
-      <c r="O72" s="21" t="inlineStr">
-        <is>
-          <t>Fissura dimensional massiva</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="21" t="inlineStr">
-        <is>
-          <t>NovaBorealis</t>
-        </is>
-      </c>
-      <c r="B73" s="21" t="inlineStr">
-        <is>
-          <t>OFF_NovaBorealis</t>
-        </is>
-      </c>
-      <c r="C73" s="21" t="inlineStr">
-        <is>
-          <t>Aurora Devastadora</t>
-        </is>
-      </c>
-      <c r="D73" s="21" t="n">
-        <v>55</v>
-      </c>
-      <c r="E73" s="21" t="inlineStr">
-        <is>
-          <t>Supreme</t>
-        </is>
-      </c>
-      <c r="F73" s="21" t="inlineStr">
-        <is>
-          <t>AoE</t>
-        </is>
-      </c>
-      <c r="G73" s="21" t="inlineStr"/>
-      <c r="H73" s="22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I73" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J73" s="21" t="inlineStr"/>
-      <c r="K73" s="22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L73" s="21" t="inlineStr"/>
-      <c r="M73" s="21" t="inlineStr">
-        <is>
-          <t>Water×2+Wind+Lightning</t>
-        </is>
-      </c>
-      <c r="N73" s="21" t="inlineStr">
-        <is>
-          <t>Aurora boreal de gelo. Freeze em onda + chain stun.</t>
-        </is>
-      </c>
-      <c r="O73" s="21" t="inlineStr">
-        <is>
-          <t>Luzes no céu que descem em cascata</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="21" t="inlineStr">
-        <is>
-          <t>SolarForge</t>
-        </is>
-      </c>
-      <c r="B74" s="21" t="inlineStr">
-        <is>
-          <t>OFF_SolarForge</t>
-        </is>
-      </c>
-      <c r="C74" s="21" t="inlineStr">
-        <is>
-          <t>Forja Solar</t>
-        </is>
-      </c>
-      <c r="D74" s="21" t="n">
-        <v>55</v>
-      </c>
-      <c r="E74" s="21" t="inlineStr">
-        <is>
-          <t>Supreme</t>
-        </is>
-      </c>
-      <c r="F74" s="21" t="inlineStr">
-        <is>
-          <t>Beam</t>
-        </is>
-      </c>
-      <c r="G74" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H74" s="21" t="inlineStr"/>
-      <c r="I74" s="21" t="inlineStr"/>
-      <c r="J74" s="22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K74" s="22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L74" s="21" t="inlineStr"/>
-      <c r="M74" s="21" t="inlineStr">
-        <is>
-          <t>Fire×2+Earth+Lightning</t>
-        </is>
-      </c>
-      <c r="N74" s="21" t="inlineStr">
-        <is>
-          <t>Raio de estrela. Perfura tudo, dano máximo.</t>
-        </is>
-      </c>
-      <c r="O74" s="21" t="inlineStr">
-        <is>
-          <t>Feixe dourado destruidor</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="21" t="inlineStr">
-        <is>
-          <t>VoidSingularity</t>
-        </is>
-      </c>
-      <c r="B75" s="21" t="inlineStr">
-        <is>
-          <t>OFF_VoidSingularity</t>
-        </is>
-      </c>
-      <c r="C75" s="21" t="inlineStr">
-        <is>
-          <t>Singularidade Void</t>
-        </is>
-      </c>
-      <c r="D75" s="21" t="n">
-        <v>55</v>
-      </c>
-      <c r="E75" s="21" t="inlineStr">
-        <is>
-          <t>Supreme</t>
-        </is>
-      </c>
-      <c r="F75" s="21" t="inlineStr">
-        <is>
-          <t>AoE</t>
-        </is>
-      </c>
-      <c r="G75" s="21" t="inlineStr"/>
-      <c r="H75" s="21" t="inlineStr"/>
-      <c r="I75" s="22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J75" s="21" t="inlineStr"/>
-      <c r="K75" s="22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L75" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M75" s="21" t="inlineStr">
-        <is>
-          <t>Reality×2+Lightning+Water</t>
-        </is>
-      </c>
-      <c r="N75" s="21" t="inlineStr">
-        <is>
-          <t>Buraco negro real. Puxa tudo por 3s, depois colapsa.</t>
-        </is>
-      </c>
-      <c r="O75" s="21" t="inlineStr">
-        <is>
-          <t>Ponto negro com disco de acreção</t>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Fire, Wind, Water, Earth, Lightning, Reality</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>A convergência suprema de todas as forças. O feitiço definitivo.</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Explosão esférica com todas as cores elementais expandindo</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5325,7 @@
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
@@ -5884,7 +5365,7 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
@@ -5924,7 +5405,7 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
@@ -5964,7 +5445,7 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -6004,7 +5485,7 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
@@ -6044,7 +5525,7 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
@@ -6084,7 +5565,7 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
@@ -6124,7 +5605,7 @@
         </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
@@ -6164,7 +5645,7 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
@@ -6204,7 +5685,7 @@
         </is>
       </c>
       <c r="D12" s="13" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
@@ -6244,7 +5725,7 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
@@ -6284,7 +5765,7 @@
         </is>
       </c>
       <c r="D14" s="13" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
@@ -6324,7 +5805,7 @@
         </is>
       </c>
       <c r="D15" s="23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
@@ -6364,7 +5845,7 @@
         </is>
       </c>
       <c r="D16" s="23" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
@@ -6404,7 +5885,7 @@
         </is>
       </c>
       <c r="D17" s="23" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
@@ -6550,7 +6031,7 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
@@ -6590,7 +6071,7 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
@@ -6630,7 +6111,7 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
@@ -6670,7 +6151,7 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
@@ -6710,7 +6191,7 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
@@ -6750,7 +6231,7 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -6790,7 +6271,7 @@
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -6830,7 +6311,7 @@
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
@@ -6870,7 +6351,7 @@
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
@@ -6910,7 +6391,7 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
@@ -6950,7 +6431,7 @@
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
@@ -6990,7 +6471,7 @@
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
@@ -7030,7 +6511,7 @@
         </is>
       </c>
       <c r="D15" s="24" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
@@ -7070,7 +6551,7 @@
         </is>
       </c>
       <c r="D16" s="24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E16" s="24" t="inlineStr">
         <is>
@@ -7110,7 +6591,7 @@
         </is>
       </c>
       <c r="D17" s="24" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
@@ -7163,13 +6644,13 @@
           <t>📊 RESUMO DA ANÁLISE v2 — PÓS-CORREÇÃO</t>
         </is>
       </c>
-      <c r="B1" s="26" t="n"/>
-      <c r="C1" s="26" t="n"/>
-      <c r="D1" s="26" t="n"/>
-      <c r="E1" s="26" t="n"/>
-      <c r="F1" s="26" t="n"/>
-      <c r="G1" s="26" t="n"/>
-      <c r="H1" s="26" t="n"/>
+      <c r="B1" s="31" t="n"/>
+      <c r="C1" s="31" t="n"/>
+      <c r="D1" s="31" t="n"/>
+      <c r="E1" s="31" t="n"/>
+      <c r="F1" s="31" t="n"/>
+      <c r="G1" s="31" t="n"/>
+      <c r="H1" s="32" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -7294,20 +6775,19 @@
       </c>
       <c r="C10" s="26" t="n"/>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="25" t="inlineStr">
         <is>
           <t>🟢 ZERO CONFLITOS — SISTEMA LIMPO!</t>
         </is>
       </c>
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="32" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="30" t="inlineStr">
@@ -7316,7 +6796,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="30" t="inlineStr">
         <is>
@@ -7324,7 +6803,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="30" t="inlineStr">
         <is>
